--- a/macros.xlsx
+++ b/macros.xlsx
@@ -8,7 +8,7 @@
     <sheet state="visible" name="dict" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$54</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="70">
   <si>
     <t>מאכל</t>
   </si>
@@ -55,22 +55,22 @@
     <t>ולידציה</t>
   </si>
   <si>
-    <t>ביצה</t>
+    <t>יוגור פרו אחוז וחצי</t>
   </si>
   <si>
-    <t>פיתות כוסמין אנג'ל</t>
+    <t>פיתות כוסמין מלא</t>
   </si>
   <si>
     <t>עגלפפון</t>
   </si>
   <si>
-    <t>יוגור פרו אחוז וחצי</t>
+    <t>עוגית חלבון</t>
+  </si>
+  <si>
+    <t>ביצה</t>
   </si>
   <si>
     <t>שמן זית</t>
-  </si>
-  <si>
-    <t>פרגית</t>
   </si>
   <si>
     <t>בצל</t>
@@ -88,31 +88,34 @@
     <t>אורז</t>
   </si>
   <si>
-    <t>קוואקר</t>
-  </si>
-  <si>
-    <t>קוטג 5</t>
-  </si>
-  <si>
-    <t>חטיף חלבון פיסטוק</t>
+    <t>גרנולה לא מתוקה</t>
   </si>
   <si>
     <t>דבש</t>
   </si>
   <si>
-    <t>עוגית חלבון</t>
+    <t>בננה</t>
   </si>
   <si>
-    <t>פסטה אוסם</t>
+    <t>יוגורט פרו מתוק</t>
   </si>
   <si>
-    <t>_</t>
+    <t>חטיף חלבון פיסטוק</t>
   </si>
   <si>
     <t>יוגורט פרו זירו</t>
   </si>
   <si>
     <t>פסטרמה</t>
+  </si>
+  <si>
+    <t>אצבעות מוצרלה</t>
+  </si>
+  <si>
+    <t>פיתות כוסמין אנג'ל</t>
+  </si>
+  <si>
+    <t>_</t>
   </si>
   <si>
     <t>אוכל</t>
@@ -130,25 +133,16 @@
     <t>אולין בוטנים קרמל</t>
   </si>
   <si>
-    <t>אצבעות מוצרלה</t>
-  </si>
-  <si>
     <t>אצבעות עמק</t>
   </si>
   <si>
     <t>בטטה</t>
   </si>
   <si>
-    <t>בננה</t>
-  </si>
-  <si>
     <t>גזר</t>
   </si>
   <si>
     <t>גמבה</t>
-  </si>
-  <si>
-    <t>גרנולה לא מתוקה</t>
   </si>
   <si>
     <t>זית</t>
@@ -170,9 +164,6 @@
   </si>
   <si>
     <t>טופו קשה</t>
-  </si>
-  <si>
-    <t>יוגורט פרו מתוק</t>
   </si>
   <si>
     <t>כדור תמרים</t>
@@ -208,7 +199,16 @@
     <t>פיתות כוסמין לבן</t>
   </si>
   <si>
-    <t>פיתות כוסמין מלא</t>
+    <t>פסטה אוסם</t>
+  </si>
+  <si>
+    <t>פרגית</t>
+  </si>
+  <si>
+    <t>קוואקר</t>
+  </si>
+  <si>
+    <t>קוטג 5</t>
   </si>
   <si>
     <t>קטניות</t>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>תערובת ירוקים</t>
+  </si>
+  <si>
+    <t>ריבר בוט בינוני</t>
+  </si>
+  <si>
+    <t>חטיף טודיי</t>
+  </si>
+  <si>
+    <t>פיתות כוסמין לוי</t>
   </si>
 </sst>
 </file>
@@ -553,43 +562,43 @@
         <v>11</v>
       </c>
       <c r="B2" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 3, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="D2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 4, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 5, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 6, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>372.61</v>
+        <v>339.35</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>224.07</v>
+        <v>196.9</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>82.09</v>
+        <v>54.87</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3108.2</v>
+        <v>2649.59</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>3125.53</v>
+        <v>2638.83</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -601,19 +610,19 @@
       </c>
       <c r="C3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 3, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>37.4</v>
       </c>
       <c r="D3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 4, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>8.8</v>
       </c>
       <c r="E3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 5, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="F3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 6, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -621,11 +630,11 @@
         <v>13</v>
       </c>
       <c r="B4" s="3">
-        <v>180.0</v>
+        <v>200.0</v>
       </c>
       <c r="C4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 3, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 4, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
@@ -637,7 +646,7 @@
       </c>
       <c r="F4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 6, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -645,23 +654,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 3, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 4, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 5, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 6, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -669,31 +678,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="3">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="C6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 3, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 4, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 5, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="F6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 6, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>41.5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="C7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 3, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
@@ -705,11 +714,11 @@
       </c>
       <c r="E7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 5, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>9.2</v>
+        <v>6.44</v>
       </c>
       <c r="F7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 6, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>83</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -717,7 +726,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="C8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 3, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
@@ -725,15 +734,15 @@
       </c>
       <c r="D8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 4, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 5, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="F8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 6, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>175</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -741,23 +750,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>150.0</v>
+        <v>180.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>14.01</v>
+        <v>16.812</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -765,23 +774,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>200.0</v>
+        <v>390.0</v>
       </c>
       <c r="C10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>3.4</v>
+        <v>6.63</v>
       </c>
       <c r="E10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="F10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>172</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -789,7 +798,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>170.0</v>
+        <v>193.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -797,15 +806,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>42.5</v>
+        <v>48.25</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4.25</v>
+        <v>4.825</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>204</v>
+        <v>231.6</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -813,23 +822,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>35.2</v>
+        <v>31.68</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>176.5</v>
+        <v>158.85</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -837,15 +846,15 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>39</v>
+        <v>35.1</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>4.4</v>
+        <v>3.96</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
@@ -853,7 +862,7 @@
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>175</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -861,23 +870,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>34.5</v>
+        <v>15.54</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>5.5</v>
+        <v>4.41</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>187</v>
+        <v>115.2</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -886,11 +895,11 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="C15" s="4">
         <f>VLOOKUP($A15, dict!$A:$F, 3, false) * $B15 / VLOOKUP($A15, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4">
         <f>VLOOKUP($A15, dict!$A:$F, 4, false) * $B15 / VLOOKUP($A15, dict!$A:$F, 2, false)</f>
@@ -902,72 +911,74 @@
       </c>
       <c r="F15" s="4">
         <f>VLOOKUP($A15, dict!$A:$F, 6, false) * $B15 / VLOOKUP($A15, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 3, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>21.7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 4, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 5, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 6, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>212</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="3">
-        <v>10.0</v>
+        <v>127.0</v>
       </c>
       <c r="C17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 3, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>8</v>
+        <v>29.718</v>
       </c>
       <c r="D17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 4, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 5, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="F17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 6, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>32</v>
-      </c>
+        <v>116.84</v>
+      </c>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 3, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="D18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 4, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 5, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
@@ -975,7 +986,7 @@
       </c>
       <c r="F18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 6, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -983,23 +994,23 @@
         <v>26</v>
       </c>
       <c r="B19" s="3">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="C19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 3, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 4, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 5, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 6, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1007,11 +1018,11 @@
         <v>13</v>
       </c>
       <c r="B20" s="5">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="C20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 3, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="D20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 4, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
@@ -1023,63 +1034,63 @@
       </c>
       <c r="F20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 6, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5">
-        <v>180.0</v>
+        <v>1.0</v>
       </c>
       <c r="C21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 3, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="D21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 4, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 5, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 6, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>216</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>71</v>
+        <v>5.5</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>349</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1087,15 +1098,15 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>9.2</v>
+        <v>8.6</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>83</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -1107,24 +1118,43 @@
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>37.4</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>8.8</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>28</v>
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="C25" s="4">
+        <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
+        <v>8</v>
+      </c>
+      <c r="D25" s="4">
+        <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <f>VLOOKUP($A25, dict!$A:$F, 5, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
+        <v>32</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -4116,7 +4146,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>110.0</v>
@@ -4160,7 +4190,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -4184,7 +4214,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -4232,7 +4262,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -4256,7 +4286,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -7260,10 +7290,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7278,12 +7308,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -7303,7 +7333,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -7321,13 +7351,13 @@
         <v>110.0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G54" si="1">4*C3 + 4*D3 + 9*E3</f>
+        <f t="shared" ref="G3:G57" si="1">4*C3 + 4*D3 + 9*E3</f>
         <v>113</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>1.0</v>
@@ -7375,7 +7405,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4">
         <v>1.0</v>
@@ -7447,7 +7477,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>1.0</v>
@@ -7471,7 +7501,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4">
         <v>100.0</v>
@@ -7519,7 +7549,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5">
         <v>100.0</v>
@@ -7543,7 +7573,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
         <v>100.0</v>
@@ -7567,7 +7597,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7591,7 +7621,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="5">
         <v>100.0</v>
@@ -7615,7 +7645,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5">
         <v>4.0</v>
@@ -7663,7 +7693,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5">
         <v>1.0</v>
@@ -7687,7 +7717,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5">
         <v>1.0</v>
@@ -7711,7 +7741,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5">
         <v>1.0</v>
@@ -7735,7 +7765,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7759,7 +7789,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7783,7 +7813,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" s="5">
         <v>100.0</v>
@@ -7807,7 +7837,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7831,7 +7861,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7855,7 +7885,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4">
         <v>1.0</v>
@@ -7879,7 +7909,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4">
         <v>1.0</v>
@@ -7903,7 +7933,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -7951,7 +7981,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B30" s="5">
         <v>100.0</v>
@@ -7975,7 +8005,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B31" s="5">
         <v>100.0</v>
@@ -7999,7 +8029,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B32" s="5">
         <v>1.0</v>
@@ -8023,7 +8053,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8047,7 +8077,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8071,7 +8101,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B35" s="5">
         <v>100.0</v>
@@ -8095,7 +8125,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8143,7 +8173,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B38" s="5">
         <v>1.0</v>
@@ -8167,7 +8197,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8191,7 +8221,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B40" s="5">
         <v>100.0</v>
@@ -8215,7 +8245,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B41" s="4">
         <v>100.0</v>
@@ -8239,7 +8269,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B42" s="5">
         <v>100.0</v>
@@ -8263,7 +8293,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8287,7 +8317,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B44" s="5">
         <v>100.0</v>
@@ -8311,7 +8341,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>
@@ -8335,7 +8365,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B46" s="4">
         <v>100.0</v>
@@ -8359,7 +8389,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B47" s="4">
         <v>100.0</v>
@@ -8383,7 +8413,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B48" s="5">
         <v>100.0</v>
@@ -8479,7 +8509,7 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B52" s="4">
         <v>100.0</v>
@@ -8549,9 +8579,78 @@
         <v>87.7</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="C55" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="D55" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="E55" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F55" s="5">
+        <v>455.0</v>
+      </c>
+      <c r="G55" s="4">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="C56" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="D56" s="5">
+        <v>18.0</v>
+      </c>
+      <c r="E56" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="F56" s="5">
+        <v>185.0</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="1"/>
+        <v>164.8</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="C57" s="5">
+        <v>29.8</v>
+      </c>
+      <c r="D57" s="5">
+        <v>12.4</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F57" s="5">
+        <v>216.0</v>
+      </c>
+      <c r="G57" s="4">
+        <f t="shared" si="1"/>
+        <v>176.9</v>
+      </c>
+    </row>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -9497,9 +9596,9 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$G$54">
-    <sortState ref="A1:G54">
-      <sortCondition ref="A1:A54"/>
+  <autoFilter ref="$A$1:$G$57">
+    <sortState ref="A1:G57">
+      <sortCondition ref="A1:A57"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -8,7 +8,7 @@
     <sheet state="visible" name="dict" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$57</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$59</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>מאכל</t>
   </si>
@@ -55,7 +55,7 @@
     <t>ולידציה</t>
   </si>
   <si>
-    <t>יוגור פרו אחוז וחצי</t>
+    <t>יוגורט פרו זירו</t>
   </si>
   <si>
     <t>פיתות כוסמין מלא</t>
@@ -88,7 +88,7 @@
     <t>אורז</t>
   </si>
   <si>
-    <t>גרנולה לא מתוקה</t>
+    <t xml:space="preserve">גרנולה שוקולד </t>
   </si>
   <si>
     <t>דבש</t>
@@ -103,16 +103,16 @@
     <t>חטיף חלבון פיסטוק</t>
   </si>
   <si>
-    <t>יוגורט פרו זירו</t>
-  </si>
-  <si>
-    <t>פסטרמה</t>
+    <t>גיינר</t>
   </si>
   <si>
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
     <t>פיתות כוסמין אנג'ל</t>
+  </si>
+  <si>
+    <t>פסטרמה</t>
   </si>
   <si>
     <t>_</t>
@@ -145,6 +145,9 @@
     <t>גמבה</t>
   </si>
   <si>
+    <t>גרנולה לא מתוקה</t>
+  </si>
+  <si>
     <t>זית</t>
   </si>
   <si>
@@ -164,6 +167,9 @@
   </si>
   <si>
     <t>טופו קשה</t>
+  </si>
+  <si>
+    <t>יוגור פרו אחוז וחצי</t>
   </si>
   <si>
     <t>כדור תמרים</t>
@@ -566,7 +572,7 @@
       </c>
       <c r="C2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 3, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="D2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 4, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
@@ -574,31 +580,31 @@
       </c>
       <c r="E2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 5, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 6, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>339.35</v>
+        <v>364.6288</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>196.9</v>
+        <v>178.664</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>54.87</v>
+        <v>45.293</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2649.59</v>
+        <v>2613.85</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2638.83</v>
+        <v>2580.8082</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -725,9 +731,7 @@
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3">
-        <v>5.0</v>
-      </c>
+      <c r="B8" s="3"/>
       <c r="C8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 3, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
         <v>0</v>
@@ -738,11 +742,11 @@
       </c>
       <c r="E8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 5, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 6, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>41.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -750,23 +754,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>180.0</v>
+        <v>162.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>16.812</v>
+        <v>15.1308</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>1.98</v>
+        <v>1.782</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.18</v>
+        <v>0.162</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>72</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -774,23 +778,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>390.0</v>
+        <v>356.0</v>
       </c>
       <c r="C10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>78</v>
+        <v>71.2</v>
       </c>
       <c r="D10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>6.63</v>
+        <v>6.052</v>
       </c>
       <c r="E10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.39</v>
+        <v>0.356</v>
       </c>
       <c r="F10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>335.4</v>
+        <v>306.16</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -798,7 +802,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>193.0</v>
+        <v>170.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -806,15 +810,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>48.25</v>
+        <v>42.5</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4.825</v>
+        <v>4.25</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>231.6</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -874,19 +878,19 @@
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>15.54</v>
+        <v>18.9</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4.41</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>115.2</v>
+        <v>130.5</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -1039,7 +1043,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B21" s="5">
         <v>1.0</v>
@@ -1063,31 +1067,31 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>120</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5">
         <v>2.0</v>
@@ -4146,7 +4150,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>110.0</v>
@@ -4190,7 +4194,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -4262,7 +4266,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -7351,7 +7355,7 @@
         <v>110.0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G57" si="1">4*C3 + 4*D3 + 9*E3</f>
+        <f t="shared" ref="G3:G59" si="1">4*C3 + 4*D3 + 9*E3</f>
         <v>113</v>
       </c>
     </row>
@@ -7405,7 +7409,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4">
         <v>1.0</v>
@@ -7597,7 +7601,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7645,7 +7649,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5">
         <v>4.0</v>
@@ -7693,7 +7697,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5">
         <v>1.0</v>
@@ -7741,7 +7745,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="5">
         <v>1.0</v>
@@ -7765,7 +7769,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7789,7 +7793,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7813,7 +7817,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5">
         <v>100.0</v>
@@ -7837,7 +7841,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7861,7 +7865,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7885,7 +7889,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B26" s="4">
         <v>1.0</v>
@@ -7933,7 +7937,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -7981,7 +7985,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" s="5">
         <v>100.0</v>
@@ -8005,7 +8009,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B31" s="5">
         <v>100.0</v>
@@ -8029,7 +8033,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B32" s="5">
         <v>1.0</v>
@@ -8053,7 +8057,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8077,7 +8081,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8101,7 +8105,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B35" s="5">
         <v>100.0</v>
@@ -8125,7 +8129,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8197,7 +8201,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8221,7 +8225,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B40" s="5">
         <v>100.0</v>
@@ -8245,7 +8249,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" s="4">
         <v>100.0</v>
@@ -8269,7 +8273,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B42" s="5">
         <v>100.0</v>
@@ -8317,7 +8321,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B44" s="5">
         <v>100.0</v>
@@ -8341,7 +8345,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>
@@ -8365,7 +8369,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B46" s="4">
         <v>100.0</v>
@@ -8389,7 +8393,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B47" s="4">
         <v>100.0</v>
@@ -8413,7 +8417,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B48" s="5">
         <v>100.0</v>
@@ -8437,7 +8441,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B49" s="4">
         <v>100.0</v>
@@ -8461,7 +8465,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B50" s="5">
         <v>100.0</v>
@@ -8485,7 +8489,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B51" s="4">
         <v>100.0</v>
@@ -8533,7 +8537,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B53" s="4">
         <v>100.0</v>
@@ -8581,7 +8585,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B55" s="5">
         <v>1.0</v>
@@ -8605,7 +8609,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B56" s="5">
         <v>1.0</v>
@@ -8629,7 +8633,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B57" s="5">
         <v>100.0</v>
@@ -8651,8 +8655,54 @@
         <v>176.9</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="C58" s="5">
+        <v>72.0</v>
+      </c>
+      <c r="D58" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="E58" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="F58" s="5">
+        <v>397.0</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="1"/>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="C59" s="5">
+        <v>63.0</v>
+      </c>
+      <c r="D59" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="E59" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F59" s="5">
+        <v>435.0</v>
+      </c>
+      <c r="G59" s="4">
+        <f t="shared" si="1"/>
+        <v>423</v>
+      </c>
+    </row>
     <row r="60" ht="15.75" customHeight="1"/>
     <row r="61" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1"/>
@@ -9596,9 +9646,9 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$G$57">
-    <sortState ref="A1:G57">
-      <sortCondition ref="A1:A57"/>
+  <autoFilter ref="$A$1:$G$59">
+    <sortState ref="A1:G59">
+      <sortCondition ref="A1:A59"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -731,7 +731,9 @@
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <v>0.0</v>
+      </c>
       <c r="C8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 3, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
         <v>0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>364.6288</v>
+        <v>356.6288</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
@@ -600,11 +600,11 @@
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2613.85</v>
+        <v>2581.85</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2580.8082</v>
+        <v>2548.8082</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -1144,11 +1144,11 @@
         <v>23</v>
       </c>
       <c r="B25" s="5">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>356.6288</v>
+        <v>364.6288</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
@@ -600,11 +600,11 @@
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2581.85</v>
+        <v>2613.85</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2548.8082</v>
+        <v>2580.8082</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -1144,11 +1144,11 @@
         <v>23</v>
       </c>
       <c r="B25" s="5">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>364.6288</v>
+        <v>363.6748</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>178.664</v>
+        <v>179.254</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>45.293</v>
+        <v>46.638</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2613.85</v>
+        <v>2628.83</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2580.8082</v>
+        <v>2591.4572</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -876,23 +876,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>18.9</v>
+        <v>25.2</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>130.5</v>
+        <v>174</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -951,23 +951,23 @@
         <v>24</v>
       </c>
       <c r="B17" s="3">
-        <v>127.0</v>
+        <v>96.0</v>
       </c>
       <c r="C17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 3, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>29.718</v>
+        <v>22.464</v>
       </c>
       <c r="D17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 4, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="E17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 5, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>0.635</v>
+        <v>0.48</v>
       </c>
       <c r="F17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 6, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>116.84</v>
+        <v>88.32</v>
       </c>
       <c r="G17" s="4"/>
     </row>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -58,7 +58,7 @@
     <t>יוגורט פרו זירו</t>
   </si>
   <si>
-    <t>פיתות כוסמין מלא</t>
+    <t>פיתות כוסמין אנג'ל</t>
   </si>
   <si>
     <t>עגלפפון</t>
@@ -109,7 +109,7 @@
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
-    <t>פיתות כוסמין אנג'ל</t>
+    <t>פיתות כוסמין מלא</t>
   </si>
   <si>
     <t>פסטרמה</t>
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>363.6748</v>
+        <v>368.0748</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>179.254</v>
+        <v>181.014</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>46.638</v>
+        <v>46.418</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2628.83</v>
+        <v>2648.63</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2591.4572</v>
+        <v>2614.1172</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -616,19 +616,19 @@
       </c>
       <c r="C3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 3, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>37.4</v>
+        <v>41.8</v>
       </c>
       <c r="D3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 4, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>8.8</v>
+        <v>10.56</v>
       </c>
       <c r="E3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 5, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="F3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 6, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>217.8</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5">
         <v>110.0</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3">
         <v>110.0</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B41" s="4">
         <v>100.0</v>
@@ -8299,7 +8299,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -109,9 +109,6 @@
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
-    <t>פיתות כוסמין מלא</t>
-  </si>
-  <si>
     <t>פסטרמה</t>
   </si>
   <si>
@@ -203,6 +200,9 @@
   </si>
   <si>
     <t>פיתות כוסמין לבן</t>
+  </si>
+  <si>
+    <t>פיתות כוסמין מלא</t>
   </si>
   <si>
     <t>פסטה אוסם</t>
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>368.0748</v>
+        <v>372.4748</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>181.014</v>
+        <v>182.774</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>46.418</v>
+        <v>46.198</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2648.63</v>
+        <v>2668.43</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2614.1172</v>
+        <v>2636.7772</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -1117,26 +1117,26 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B24" s="5">
         <v>110.0</v>
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>37.4</v>
+        <v>41.8</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>8.8</v>
+        <v>10.56</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>217.8</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -4268,7 +4268,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -7296,10 +7296,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7314,12 +7314,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -7339,7 +7339,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -7363,7 +7363,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5">
         <v>1.0</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -7459,7 +7459,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5">
         <v>100.0</v>
@@ -7555,7 +7555,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5">
         <v>100.0</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4">
         <v>100.0</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5">
         <v>4.0</v>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5">
         <v>1.0</v>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5">
         <v>1.0</v>
@@ -7771,7 +7771,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="5">
         <v>100.0</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7867,7 +7867,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" s="5">
         <v>100.0</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" s="5">
         <v>100.0</v>
@@ -8035,7 +8035,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32" s="5">
         <v>1.0</v>
@@ -8059,7 +8059,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="5">
         <v>100.0</v>
@@ -8131,7 +8131,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="5">
         <v>100.0</v>
@@ -8275,7 +8275,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" s="5">
         <v>100.0</v>
@@ -8299,7 +8299,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -109,6 +109,9 @@
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
+    <t>פיתות כוסמין מלא</t>
+  </si>
+  <si>
     <t>פסטרמה</t>
   </si>
   <si>
@@ -200,9 +203,6 @@
   </si>
   <si>
     <t>פיתות כוסמין לבן</t>
-  </si>
-  <si>
-    <t>פיתות כוסמין מלא</t>
   </si>
   <si>
     <t>פסטה אוסם</t>
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>372.4748</v>
+        <v>335.9144</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>182.774</v>
+        <v>194.492</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>46.198</v>
+        <v>65.974</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2668.43</v>
+        <v>2735.85</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2636.7772</v>
+        <v>2715.3916</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -660,23 +660,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="3">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="C5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 3, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="D5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 4, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 5, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="F5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 6, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -708,7 +708,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="C7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 3, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
@@ -720,11 +720,11 @@
       </c>
       <c r="E7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 5, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>6.44</v>
+        <v>9.2</v>
       </c>
       <c r="F7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 6, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>58.1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -732,7 +732,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="C8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 3, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
@@ -744,11 +744,11 @@
       </c>
       <c r="E8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 5, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="F8" s="4">
         <f>VLOOKUP($A8, dict!$A:$F, 6, false) * $B8 / VLOOKUP($A8, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -756,23 +756,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>162.0</v>
+        <v>156.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>15.1308</v>
+        <v>14.5704</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>1.782</v>
+        <v>1.716</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>64.8</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -780,23 +780,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>356.0</v>
+        <v>288.0</v>
       </c>
       <c r="C10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>71.2</v>
+        <v>57.6</v>
       </c>
       <c r="D10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>6.052</v>
+        <v>4.896</v>
       </c>
       <c r="E10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.356</v>
+        <v>0.288</v>
       </c>
       <c r="F10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>306.16</v>
+        <v>247.68</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -926,11 +926,11 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="C16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 3, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 4, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
@@ -942,7 +942,7 @@
       </c>
       <c r="F16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 6, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -1024,11 +1024,11 @@
         <v>13</v>
       </c>
       <c r="B20" s="5">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="C20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 3, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 4, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 6, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1072,23 +1072,23 @@
         <v>27</v>
       </c>
       <c r="B22" s="5">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>36</v>
+        <v>28.8</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>198.5</v>
+        <v>158.8</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1096,7 +1096,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="5">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1104,51 +1104,49 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>10.4</v>
+        <v>20.8</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>8.6</v>
+        <v>17.2</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>118</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5">
-        <v>110.0</v>
+        <v>90.0</v>
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>30.6</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>7.2</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>178.2</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="5">
-        <v>10.0</v>
-      </c>
+      <c r="B25" s="5"/>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
@@ -1160,7 +1158,7 @@
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -4268,7 +4266,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -4292,7 +4290,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -7296,10 +7294,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7314,12 +7312,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -7339,7 +7337,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -7363,7 +7361,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>1.0</v>
@@ -7435,7 +7433,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -7459,7 +7457,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5">
         <v>100.0</v>
@@ -7555,7 +7553,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5">
         <v>100.0</v>
@@ -7579,7 +7577,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
         <v>100.0</v>
@@ -7603,7 +7601,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7651,7 +7649,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5">
         <v>4.0</v>
@@ -7699,7 +7697,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5">
         <v>1.0</v>
@@ -7747,7 +7745,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="5">
         <v>1.0</v>
@@ -7771,7 +7769,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7795,7 +7793,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7819,7 +7817,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5">
         <v>100.0</v>
@@ -7843,7 +7841,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7867,7 +7865,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7939,7 +7937,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -7987,7 +7985,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="5">
         <v>100.0</v>
@@ -8011,7 +8009,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="5">
         <v>100.0</v>
@@ -8035,7 +8033,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B32" s="5">
         <v>1.0</v>
@@ -8059,7 +8057,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8083,7 +8081,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8107,7 +8105,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="5">
         <v>100.0</v>
@@ -8131,7 +8129,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8203,7 +8201,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8227,7 +8225,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" s="5">
         <v>100.0</v>
@@ -8275,7 +8273,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B42" s="5">
         <v>100.0</v>
@@ -8299,7 +8297,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8347,7 +8345,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>335.9144</v>
+        <v>411.624</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>194.492</v>
+        <v>193.232</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>65.974</v>
+        <v>54.706</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2735.85</v>
+        <v>2956.33</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2715.3916</v>
+        <v>2911.778</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -660,23 +660,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="3">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="C5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 3, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 4, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 5, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 6, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -708,7 +708,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="C7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 3, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
@@ -720,11 +720,11 @@
       </c>
       <c r="E7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 5, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>9.2</v>
+        <v>6.44</v>
       </c>
       <c r="F7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 6, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>83</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -756,23 +756,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>156.0</v>
+        <v>200.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>14.5704</v>
+        <v>18.68</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>1.716</v>
+        <v>2.2</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.156</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>62.4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -780,23 +780,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>288.0</v>
+        <v>256.0</v>
       </c>
       <c r="C10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>57.6</v>
+        <v>51.2</v>
       </c>
       <c r="D10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>4.896</v>
+        <v>4.352</v>
       </c>
       <c r="E10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.288</v>
+        <v>0.256</v>
       </c>
       <c r="F10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>247.68</v>
+        <v>220.16</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -804,7 +804,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>170.0</v>
+        <v>160.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -812,15 +812,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -1024,11 +1024,11 @@
         <v>13</v>
       </c>
       <c r="B20" s="5">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="C20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 3, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="D20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 4, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 6, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1072,23 +1072,23 @@
         <v>27</v>
       </c>
       <c r="B22" s="5">
-        <v>40.0</v>
+        <v>150.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>28.8</v>
+        <v>108</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>158.8</v>
+        <v>595.5</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1096,7 +1096,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="5">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1104,15 +1104,15 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>20.8</v>
+        <v>10.4</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>17.2</v>
+        <v>8.6</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>236</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -1120,30 +1120,32 @@
         <v>29</v>
       </c>
       <c r="B24" s="5">
-        <v>90.0</v>
+        <v>110.0</v>
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>30.6</v>
+        <v>37.4</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>7.2</v>
+        <v>8.8</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>178.2</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0.0</v>
+      </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
         <v>0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -100,9 +100,6 @@
     <t>יוגורט פרו מתוק</t>
   </si>
   <si>
-    <t>חטיף חלבון פיסטוק</t>
-  </si>
-  <si>
     <t>גיינר</t>
   </si>
   <si>
@@ -110,6 +107,9 @@
   </si>
   <si>
     <t>פיתות כוסמין מלא</t>
+  </si>
+  <si>
+    <t>קוואקר</t>
   </si>
   <si>
     <t>פסטרמה</t>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>חטיף חלבון מקסברנר</t>
+  </si>
+  <si>
+    <t>חטיף חלבון פיסטוק</t>
   </si>
   <si>
     <t>חטיף נטור ואלי</t>
@@ -209,9 +212,6 @@
   </si>
   <si>
     <t>פרגית</t>
-  </si>
-  <si>
-    <t>קוואקר</t>
   </si>
   <si>
     <t>קוטג 5</t>
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>411.624</v>
+        <v>421.624</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>193.232</v>
+        <v>203.232</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>54.706</v>
+        <v>65.306</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>2956.33</v>
+        <v>3120.83</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2911.778</v>
+        <v>3087.178</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -997,14 +997,14 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="C19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 3, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 4, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 6, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1069,34 +1069,34 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="5">
-        <v>150.0</v>
+        <v>120.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>108</v>
+        <v>86.4</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>595.5</v>
+        <v>476.4</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="5">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1104,20 +1104,20 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>10.4</v>
+        <v>20.8</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>8.6</v>
+        <v>17.2</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>118</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5">
         <v>110.0</v>
@@ -1141,26 +1141,26 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="5">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="E25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 5, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -7411,7 +7411,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4">
         <v>1.0</v>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5">
         <v>1.0</v>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="5">
         <v>1.0</v>
@@ -7771,7 +7771,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="5">
         <v>100.0</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7867,7 +7867,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="5">
         <v>100.0</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="5">
         <v>100.0</v>
@@ -8035,7 +8035,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="5">
         <v>1.0</v>
@@ -8059,7 +8059,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="5">
         <v>100.0</v>
@@ -8131,7 +8131,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B40" s="5">
         <v>100.0</v>
@@ -8275,7 +8275,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" s="5">
         <v>100.0</v>
@@ -8299,7 +8299,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" s="5">
         <v>100.0</v>
@@ -8371,7 +8371,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B46" s="4">
         <v>100.0</v>
@@ -8395,7 +8395,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="B47" s="4">
         <v>100.0</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B58" s="5">
         <v>100.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -588,23 +588,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>421.624</v>
+        <v>384.9488</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>203.232</v>
+        <v>212.072</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>65.306</v>
+        <v>63.802</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3120.83</v>
+        <v>3014.65</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>3087.178</v>
+        <v>2962.3012</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -756,23 +756,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>200.0</v>
+        <v>232.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>18.68</v>
+        <v>21.6688</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.2</v>
+        <v>2.552</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.2</v>
+        <v>0.232</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>80</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -780,23 +780,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>256.0</v>
+        <v>200.0</v>
       </c>
       <c r="C10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>51.2</v>
+        <v>40</v>
       </c>
       <c r="D10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>4.352</v>
+        <v>3.4</v>
       </c>
       <c r="E10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.256</v>
+        <v>0.2</v>
       </c>
       <c r="F10" s="4">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>220.16</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -804,7 +804,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>160.0</v>
+        <v>200.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -812,15 +812,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>192</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -951,23 +951,23 @@
         <v>24</v>
       </c>
       <c r="B17" s="3">
-        <v>96.0</v>
+        <v>0.0</v>
       </c>
       <c r="C17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 3, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>22.464</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 4, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 5, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
         <f>VLOOKUP($A17, dict!$A:$F, 6, false) * $B17 / VLOOKUP($A17, dict!$A:$F, 2, false)</f>
-        <v>88.32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -1072,23 +1072,23 @@
         <v>26</v>
       </c>
       <c r="B22" s="5">
-        <v>120.0</v>
+        <v>150.0</v>
       </c>
       <c r="C22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 3, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>86.4</v>
+        <v>108</v>
       </c>
       <c r="D22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 4, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>19.2</v>
+        <v>24</v>
       </c>
       <c r="E22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 5, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F22" s="4">
         <f>VLOOKUP($A22, dict!$A:$F, 6, false) * $B22 / VLOOKUP($A22, dict!$A:$F, 2, false)</f>
-        <v>476.4</v>
+        <v>595.5</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1144,23 +1144,23 @@
         <v>29</v>
       </c>
       <c r="B25" s="5">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 5, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>149.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -242,6 +242,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;$&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.0"/>
@@ -273,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -287,6 +290,10 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -588,23 +595,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>384.9488</v>
+        <v>387.7014</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>212.072</v>
+        <v>211.863</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>63.802</v>
+        <v>63.717</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3014.65</v>
+        <v>3023.26</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2962.3012</v>
+        <v>2971.7106</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -756,47 +763,47 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>232.0</v>
+        <v>221.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>21.6688</v>
+        <v>20.6414</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.552</v>
+        <v>2.431</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.232</v>
+        <v>0.221</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>92.8</v>
+        <v>88.4</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="5">
+        <v>256.0</v>
+      </c>
+      <c r="C10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>40</v>
-      </c>
-      <c r="D10" s="4">
+        <v>51.2</v>
+      </c>
+      <c r="D10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>3.4</v>
-      </c>
-      <c r="E10" s="4">
+        <v>4.352</v>
+      </c>
+      <c r="E10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="4">
+        <v>0.256</v>
+      </c>
+      <c r="F10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>172</v>
+        <v>220.16</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -828,23 +835,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>31.68</v>
+        <v>28.16</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>158.85</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -852,15 +859,15 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>35.1</v>
+        <v>31.2</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
@@ -868,7 +875,7 @@
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>157.5</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -1023,7 +1030,7 @@
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="7">
         <v>100.0</v>
       </c>
       <c r="C20" s="4">
@@ -1047,7 +1054,7 @@
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="7">
         <v>1.0</v>
       </c>
       <c r="C21" s="4">
@@ -1071,7 +1078,7 @@
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="7">
         <v>150.0</v>
       </c>
       <c r="C22" s="4">
@@ -1095,7 +1102,7 @@
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="7">
         <v>4.0</v>
       </c>
       <c r="C23" s="4">
@@ -1119,7 +1126,7 @@
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="7">
         <v>110.0</v>
       </c>
       <c r="C24" s="4">
@@ -1143,7 +1150,7 @@
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="7">
         <v>0.0</v>
       </c>
       <c r="C25" s="4">
@@ -1755,2344 +1762,2344 @@
       <c r="A222" s="4"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="6"/>
+      <c r="A223" s="8"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="6"/>
+      <c r="A224" s="8"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="6"/>
+      <c r="A225" s="8"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="6"/>
+      <c r="A226" s="8"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="6"/>
+      <c r="A227" s="8"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="6"/>
+      <c r="A228" s="8"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="6"/>
+      <c r="A229" s="8"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="6"/>
+      <c r="A230" s="8"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="6"/>
+      <c r="A231" s="8"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="6"/>
+      <c r="A232" s="8"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="6"/>
+      <c r="A233" s="8"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="6"/>
+      <c r="A234" s="8"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="6"/>
+      <c r="A235" s="8"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="6"/>
+      <c r="A236" s="8"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="6"/>
+      <c r="A237" s="8"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="6"/>
+      <c r="A238" s="8"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="6"/>
+      <c r="A239" s="8"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="6"/>
+      <c r="A240" s="8"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="6"/>
+      <c r="A241" s="8"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="6"/>
+      <c r="A242" s="8"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="6"/>
+      <c r="A243" s="8"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="6"/>
+      <c r="A244" s="8"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="6"/>
+      <c r="A245" s="8"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="6"/>
+      <c r="A246" s="8"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="6"/>
+      <c r="A247" s="8"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="6"/>
+      <c r="A248" s="8"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="6"/>
+      <c r="A249" s="8"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="6"/>
+      <c r="A250" s="8"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="6"/>
+      <c r="A251" s="8"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="6"/>
+      <c r="A252" s="8"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="6"/>
+      <c r="A253" s="8"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="6"/>
+      <c r="A254" s="8"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="6"/>
+      <c r="A255" s="8"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="6"/>
+      <c r="A256" s="8"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="6"/>
+      <c r="A257" s="8"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="6"/>
+      <c r="A258" s="8"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="6"/>
+      <c r="A259" s="8"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="6"/>
+      <c r="A260" s="8"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="6"/>
+      <c r="A261" s="8"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="6"/>
+      <c r="A262" s="8"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="6"/>
+      <c r="A263" s="8"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="6"/>
+      <c r="A264" s="8"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="6"/>
+      <c r="A265" s="8"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="6"/>
+      <c r="A266" s="8"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="6"/>
+      <c r="A267" s="8"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="6"/>
+      <c r="A268" s="8"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="6"/>
+      <c r="A269" s="8"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="6"/>
+      <c r="A270" s="8"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="6"/>
+      <c r="A271" s="8"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="6"/>
+      <c r="A272" s="8"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="6"/>
+      <c r="A273" s="8"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="6"/>
+      <c r="A274" s="8"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="6"/>
+      <c r="A275" s="8"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="6"/>
+      <c r="A276" s="8"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="6"/>
+      <c r="A277" s="8"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="6"/>
+      <c r="A278" s="8"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="6"/>
+      <c r="A279" s="8"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="6"/>
+      <c r="A280" s="8"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="6"/>
+      <c r="A281" s="8"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="6"/>
+      <c r="A282" s="8"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="6"/>
+      <c r="A283" s="8"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="6"/>
+      <c r="A284" s="8"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="6"/>
+      <c r="A285" s="8"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="6"/>
+      <c r="A286" s="8"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="6"/>
+      <c r="A287" s="8"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="6"/>
+      <c r="A288" s="8"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="6"/>
+      <c r="A289" s="8"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="6"/>
+      <c r="A290" s="8"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="6"/>
+      <c r="A291" s="8"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="6"/>
+      <c r="A292" s="8"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="6"/>
+      <c r="A293" s="8"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="6"/>
+      <c r="A294" s="8"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="6"/>
+      <c r="A295" s="8"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="6"/>
+      <c r="A296" s="8"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="6"/>
+      <c r="A297" s="8"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="6"/>
+      <c r="A298" s="8"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="6"/>
+      <c r="A299" s="8"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="6"/>
+      <c r="A300" s="8"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="6"/>
+      <c r="A301" s="8"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="6"/>
+      <c r="A302" s="8"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="6"/>
+      <c r="A303" s="8"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="6"/>
+      <c r="A304" s="8"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="6"/>
+      <c r="A305" s="8"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="6"/>
+      <c r="A306" s="8"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="6"/>
+      <c r="A307" s="8"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="6"/>
+      <c r="A308" s="8"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="6"/>
+      <c r="A309" s="8"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="6"/>
+      <c r="A310" s="8"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="6"/>
+      <c r="A311" s="8"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="6"/>
+      <c r="A312" s="8"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="6"/>
+      <c r="A313" s="8"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="6"/>
+      <c r="A314" s="8"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="6"/>
+      <c r="A315" s="8"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="6"/>
+      <c r="A316" s="8"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="6"/>
+      <c r="A317" s="8"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="6"/>
+      <c r="A318" s="8"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="6"/>
+      <c r="A319" s="8"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="6"/>
+      <c r="A320" s="8"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="6"/>
+      <c r="A321" s="8"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="6"/>
+      <c r="A322" s="8"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="6"/>
+      <c r="A323" s="8"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="6"/>
+      <c r="A324" s="8"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="6"/>
+      <c r="A325" s="8"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="6"/>
+      <c r="A326" s="8"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="6"/>
+      <c r="A327" s="8"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="6"/>
+      <c r="A328" s="8"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="6"/>
+      <c r="A329" s="8"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="6"/>
+      <c r="A330" s="8"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="6"/>
+      <c r="A331" s="8"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="6"/>
+      <c r="A332" s="8"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="6"/>
+      <c r="A333" s="8"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="6"/>
+      <c r="A334" s="8"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="6"/>
+      <c r="A335" s="8"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="6"/>
+      <c r="A336" s="8"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="6"/>
+      <c r="A337" s="8"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="6"/>
+      <c r="A338" s="8"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="6"/>
+      <c r="A339" s="8"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="6"/>
+      <c r="A340" s="8"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="6"/>
+      <c r="A341" s="8"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="6"/>
+      <c r="A342" s="8"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="6"/>
+      <c r="A343" s="8"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="6"/>
+      <c r="A344" s="8"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="6"/>
+      <c r="A345" s="8"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="6"/>
+      <c r="A346" s="8"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="6"/>
+      <c r="A347" s="8"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="6"/>
+      <c r="A348" s="8"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="6"/>
+      <c r="A349" s="8"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="6"/>
+      <c r="A350" s="8"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="6"/>
+      <c r="A351" s="8"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="6"/>
+      <c r="A352" s="8"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="6"/>
+      <c r="A353" s="8"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="6"/>
+      <c r="A354" s="8"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="6"/>
+      <c r="A355" s="8"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="6"/>
+      <c r="A356" s="8"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="6"/>
+      <c r="A357" s="8"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="6"/>
+      <c r="A358" s="8"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="6"/>
+      <c r="A359" s="8"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="6"/>
+      <c r="A360" s="8"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="6"/>
+      <c r="A361" s="8"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="6"/>
+      <c r="A362" s="8"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="6"/>
+      <c r="A363" s="8"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="6"/>
+      <c r="A364" s="8"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="6"/>
+      <c r="A365" s="8"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="6"/>
+      <c r="A366" s="8"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="6"/>
+      <c r="A367" s="8"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="6"/>
+      <c r="A368" s="8"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="6"/>
+      <c r="A369" s="8"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="6"/>
+      <c r="A370" s="8"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="6"/>
+      <c r="A371" s="8"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="6"/>
+      <c r="A372" s="8"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="6"/>
+      <c r="A373" s="8"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="6"/>
+      <c r="A374" s="8"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="6"/>
+      <c r="A375" s="8"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="6"/>
+      <c r="A376" s="8"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="6"/>
+      <c r="A377" s="8"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="6"/>
+      <c r="A378" s="8"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="6"/>
+      <c r="A379" s="8"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="6"/>
+      <c r="A380" s="8"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="6"/>
+      <c r="A381" s="8"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="6"/>
+      <c r="A382" s="8"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="6"/>
+      <c r="A383" s="8"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="6"/>
+      <c r="A384" s="8"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="6"/>
+      <c r="A385" s="8"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="6"/>
+      <c r="A386" s="8"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="6"/>
+      <c r="A387" s="8"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="6"/>
+      <c r="A388" s="8"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="6"/>
+      <c r="A389" s="8"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="6"/>
+      <c r="A390" s="8"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="6"/>
+      <c r="A391" s="8"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="6"/>
+      <c r="A392" s="8"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="6"/>
+      <c r="A393" s="8"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="6"/>
+      <c r="A394" s="8"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="6"/>
+      <c r="A395" s="8"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="6"/>
+      <c r="A396" s="8"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="6"/>
+      <c r="A397" s="8"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="6"/>
+      <c r="A398" s="8"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="6"/>
+      <c r="A399" s="8"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="6"/>
+      <c r="A400" s="8"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="6"/>
+      <c r="A401" s="8"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="6"/>
+      <c r="A402" s="8"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="6"/>
+      <c r="A403" s="8"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="6"/>
+      <c r="A404" s="8"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="6"/>
+      <c r="A405" s="8"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="6"/>
+      <c r="A406" s="8"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="6"/>
+      <c r="A407" s="8"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="6"/>
+      <c r="A408" s="8"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="6"/>
+      <c r="A409" s="8"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="6"/>
+      <c r="A410" s="8"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="6"/>
+      <c r="A411" s="8"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="6"/>
+      <c r="A412" s="8"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="6"/>
+      <c r="A413" s="8"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="6"/>
+      <c r="A414" s="8"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="6"/>
+      <c r="A415" s="8"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="6"/>
+      <c r="A416" s="8"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="6"/>
+      <c r="A417" s="8"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="6"/>
+      <c r="A418" s="8"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="6"/>
+      <c r="A419" s="8"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="6"/>
+      <c r="A420" s="8"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="6"/>
+      <c r="A421" s="8"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="6"/>
+      <c r="A422" s="8"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="6"/>
+      <c r="A423" s="8"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="6"/>
+      <c r="A424" s="8"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="6"/>
+      <c r="A425" s="8"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="6"/>
+      <c r="A426" s="8"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="6"/>
+      <c r="A427" s="8"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="6"/>
+      <c r="A428" s="8"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="6"/>
+      <c r="A429" s="8"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="6"/>
+      <c r="A430" s="8"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="6"/>
+      <c r="A431" s="8"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="6"/>
+      <c r="A432" s="8"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="6"/>
+      <c r="A433" s="8"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="6"/>
+      <c r="A434" s="8"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="6"/>
+      <c r="A435" s="8"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="6"/>
+      <c r="A436" s="8"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="6"/>
+      <c r="A437" s="8"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="6"/>
+      <c r="A438" s="8"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="6"/>
+      <c r="A439" s="8"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="6"/>
+      <c r="A440" s="8"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="6"/>
+      <c r="A441" s="8"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="6"/>
+      <c r="A442" s="8"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="6"/>
+      <c r="A443" s="8"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="6"/>
+      <c r="A444" s="8"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="6"/>
+      <c r="A445" s="8"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="6"/>
+      <c r="A446" s="8"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="6"/>
+      <c r="A447" s="8"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="6"/>
+      <c r="A448" s="8"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="6"/>
+      <c r="A449" s="8"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="6"/>
+      <c r="A450" s="8"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="6"/>
+      <c r="A451" s="8"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="6"/>
+      <c r="A452" s="8"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="6"/>
+      <c r="A453" s="8"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="6"/>
+      <c r="A454" s="8"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="6"/>
+      <c r="A455" s="8"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="6"/>
+      <c r="A456" s="8"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="6"/>
+      <c r="A457" s="8"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="6"/>
+      <c r="A458" s="8"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="6"/>
+      <c r="A459" s="8"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="6"/>
+      <c r="A460" s="8"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="6"/>
+      <c r="A461" s="8"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="6"/>
+      <c r="A462" s="8"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="6"/>
+      <c r="A463" s="8"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="6"/>
+      <c r="A464" s="8"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="6"/>
+      <c r="A465" s="8"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="6"/>
+      <c r="A466" s="8"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="6"/>
+      <c r="A467" s="8"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="6"/>
+      <c r="A468" s="8"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="6"/>
+      <c r="A469" s="8"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="6"/>
+      <c r="A470" s="8"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="6"/>
+      <c r="A471" s="8"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="6"/>
+      <c r="A472" s="8"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="6"/>
+      <c r="A473" s="8"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="6"/>
+      <c r="A474" s="8"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="6"/>
+      <c r="A475" s="8"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="6"/>
+      <c r="A476" s="8"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="6"/>
+      <c r="A477" s="8"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="6"/>
+      <c r="A478" s="8"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="6"/>
+      <c r="A479" s="8"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="6"/>
+      <c r="A480" s="8"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="6"/>
+      <c r="A481" s="8"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="6"/>
+      <c r="A482" s="8"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="6"/>
+      <c r="A483" s="8"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="6"/>
+      <c r="A484" s="8"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="6"/>
+      <c r="A485" s="8"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="6"/>
+      <c r="A486" s="8"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="6"/>
+      <c r="A487" s="8"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="6"/>
+      <c r="A488" s="8"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="6"/>
+      <c r="A489" s="8"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="6"/>
+      <c r="A490" s="8"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="6"/>
+      <c r="A491" s="8"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="6"/>
+      <c r="A492" s="8"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="6"/>
+      <c r="A493" s="8"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="6"/>
+      <c r="A494" s="8"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="6"/>
+      <c r="A495" s="8"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="6"/>
+      <c r="A496" s="8"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="6"/>
+      <c r="A497" s="8"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="6"/>
+      <c r="A498" s="8"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="6"/>
+      <c r="A499" s="8"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="6"/>
+      <c r="A500" s="8"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="6"/>
+      <c r="A501" s="8"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="6"/>
+      <c r="A502" s="8"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="6"/>
+      <c r="A503" s="8"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="6"/>
+      <c r="A504" s="8"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="6"/>
+      <c r="A505" s="8"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="6"/>
+      <c r="A506" s="8"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="6"/>
+      <c r="A507" s="8"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="6"/>
+      <c r="A508" s="8"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="6"/>
+      <c r="A509" s="8"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="6"/>
+      <c r="A510" s="8"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="6"/>
+      <c r="A511" s="8"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="6"/>
+      <c r="A512" s="8"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="6"/>
+      <c r="A513" s="8"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="6"/>
+      <c r="A514" s="8"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="6"/>
+      <c r="A515" s="8"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="6"/>
+      <c r="A516" s="8"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="6"/>
+      <c r="A517" s="8"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="6"/>
+      <c r="A518" s="8"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="6"/>
+      <c r="A519" s="8"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="6"/>
+      <c r="A520" s="8"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="6"/>
+      <c r="A521" s="8"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="6"/>
+      <c r="A522" s="8"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="6"/>
+      <c r="A523" s="8"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="6"/>
+      <c r="A524" s="8"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="6"/>
+      <c r="A525" s="8"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="6"/>
+      <c r="A526" s="8"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="6"/>
+      <c r="A527" s="8"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="6"/>
+      <c r="A528" s="8"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="6"/>
+      <c r="A529" s="8"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="6"/>
+      <c r="A530" s="8"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="6"/>
+      <c r="A531" s="8"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="6"/>
+      <c r="A532" s="8"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="6"/>
+      <c r="A533" s="8"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="6"/>
+      <c r="A534" s="8"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="6"/>
+      <c r="A535" s="8"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="6"/>
+      <c r="A536" s="8"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="6"/>
+      <c r="A537" s="8"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="6"/>
+      <c r="A538" s="8"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="6"/>
+      <c r="A539" s="8"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="6"/>
+      <c r="A540" s="8"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="6"/>
+      <c r="A541" s="8"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="6"/>
+      <c r="A542" s="8"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="6"/>
+      <c r="A543" s="8"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="6"/>
+      <c r="A544" s="8"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="6"/>
+      <c r="A545" s="8"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="6"/>
+      <c r="A546" s="8"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="6"/>
+      <c r="A547" s="8"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="6"/>
+      <c r="A548" s="8"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="6"/>
+      <c r="A549" s="8"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="6"/>
+      <c r="A550" s="8"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="6"/>
+      <c r="A551" s="8"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="6"/>
+      <c r="A552" s="8"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="6"/>
+      <c r="A553" s="8"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="6"/>
+      <c r="A554" s="8"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="6"/>
+      <c r="A555" s="8"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="6"/>
+      <c r="A556" s="8"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="6"/>
+      <c r="A557" s="8"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="6"/>
+      <c r="A558" s="8"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="6"/>
+      <c r="A559" s="8"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="6"/>
+      <c r="A560" s="8"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="6"/>
+      <c r="A561" s="8"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="6"/>
+      <c r="A562" s="8"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="6"/>
+      <c r="A563" s="8"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="6"/>
+      <c r="A564" s="8"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="6"/>
+      <c r="A565" s="8"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="6"/>
+      <c r="A566" s="8"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="6"/>
+      <c r="A567" s="8"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="6"/>
+      <c r="A568" s="8"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="6"/>
+      <c r="A569" s="8"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="6"/>
+      <c r="A570" s="8"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="6"/>
+      <c r="A571" s="8"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="6"/>
+      <c r="A572" s="8"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="6"/>
+      <c r="A573" s="8"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="6"/>
+      <c r="A574" s="8"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="6"/>
+      <c r="A575" s="8"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="6"/>
+      <c r="A576" s="8"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="6"/>
+      <c r="A577" s="8"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="6"/>
+      <c r="A578" s="8"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="6"/>
+      <c r="A579" s="8"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="6"/>
+      <c r="A580" s="8"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="6"/>
+      <c r="A581" s="8"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="6"/>
+      <c r="A582" s="8"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="6"/>
+      <c r="A583" s="8"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="6"/>
+      <c r="A584" s="8"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="6"/>
+      <c r="A585" s="8"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="6"/>
+      <c r="A586" s="8"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="6"/>
+      <c r="A587" s="8"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="6"/>
+      <c r="A588" s="8"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="6"/>
+      <c r="A589" s="8"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="6"/>
+      <c r="A590" s="8"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="6"/>
+      <c r="A591" s="8"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="6"/>
+      <c r="A592" s="8"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="6"/>
+      <c r="A593" s="8"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="6"/>
+      <c r="A594" s="8"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="6"/>
+      <c r="A595" s="8"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="6"/>
+      <c r="A596" s="8"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="6"/>
+      <c r="A597" s="8"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="6"/>
+      <c r="A598" s="8"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="6"/>
+      <c r="A599" s="8"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="6"/>
+      <c r="A600" s="8"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="6"/>
+      <c r="A601" s="8"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="6"/>
+      <c r="A602" s="8"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="6"/>
+      <c r="A603" s="8"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="6"/>
+      <c r="A604" s="8"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="6"/>
+      <c r="A605" s="8"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="6"/>
+      <c r="A606" s="8"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="6"/>
+      <c r="A607" s="8"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="6"/>
+      <c r="A608" s="8"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="6"/>
+      <c r="A609" s="8"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="6"/>
+      <c r="A610" s="8"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="6"/>
+      <c r="A611" s="8"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="6"/>
+      <c r="A612" s="8"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="6"/>
+      <c r="A613" s="8"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="6"/>
+      <c r="A614" s="8"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="6"/>
+      <c r="A615" s="8"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="6"/>
+      <c r="A616" s="8"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="6"/>
+      <c r="A617" s="8"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="6"/>
+      <c r="A618" s="8"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="6"/>
+      <c r="A619" s="8"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="6"/>
+      <c r="A620" s="8"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="6"/>
+      <c r="A621" s="8"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="6"/>
+      <c r="A622" s="8"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="6"/>
+      <c r="A623" s="8"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="6"/>
+      <c r="A624" s="8"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="6"/>
+      <c r="A625" s="8"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="6"/>
+      <c r="A626" s="8"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="6"/>
+      <c r="A627" s="8"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="6"/>
+      <c r="A628" s="8"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="6"/>
+      <c r="A629" s="8"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="6"/>
+      <c r="A630" s="8"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="6"/>
+      <c r="A631" s="8"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="6"/>
+      <c r="A632" s="8"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="6"/>
+      <c r="A633" s="8"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="6"/>
+      <c r="A634" s="8"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="6"/>
+      <c r="A635" s="8"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="6"/>
+      <c r="A636" s="8"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="6"/>
+      <c r="A637" s="8"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="6"/>
+      <c r="A638" s="8"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="6"/>
+      <c r="A639" s="8"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="6"/>
+      <c r="A640" s="8"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="6"/>
+      <c r="A641" s="8"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="6"/>
+      <c r="A642" s="8"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="6"/>
+      <c r="A643" s="8"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="6"/>
+      <c r="A644" s="8"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="6"/>
+      <c r="A645" s="8"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="6"/>
+      <c r="A646" s="8"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="6"/>
+      <c r="A647" s="8"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="6"/>
+      <c r="A648" s="8"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="6"/>
+      <c r="A649" s="8"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="6"/>
+      <c r="A650" s="8"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="6"/>
+      <c r="A651" s="8"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="6"/>
+      <c r="A652" s="8"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="6"/>
+      <c r="A653" s="8"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="6"/>
+      <c r="A654" s="8"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="6"/>
+      <c r="A655" s="8"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="6"/>
+      <c r="A656" s="8"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="6"/>
+      <c r="A657" s="8"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="6"/>
+      <c r="A658" s="8"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="6"/>
+      <c r="A659" s="8"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="6"/>
+      <c r="A660" s="8"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="6"/>
+      <c r="A661" s="8"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="6"/>
+      <c r="A662" s="8"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="6"/>
+      <c r="A663" s="8"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="6"/>
+      <c r="A664" s="8"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="6"/>
+      <c r="A665" s="8"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="6"/>
+      <c r="A666" s="8"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="6"/>
+      <c r="A667" s="8"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="6"/>
+      <c r="A668" s="8"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="6"/>
+      <c r="A669" s="8"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="6"/>
+      <c r="A670" s="8"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="6"/>
+      <c r="A671" s="8"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="6"/>
+      <c r="A672" s="8"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="6"/>
+      <c r="A673" s="8"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="6"/>
+      <c r="A674" s="8"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="6"/>
+      <c r="A675" s="8"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="6"/>
+      <c r="A676" s="8"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="6"/>
+      <c r="A677" s="8"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="6"/>
+      <c r="A678" s="8"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="6"/>
+      <c r="A679" s="8"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="6"/>
+      <c r="A680" s="8"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="6"/>
+      <c r="A681" s="8"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="6"/>
+      <c r="A682" s="8"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="6"/>
+      <c r="A683" s="8"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="6"/>
+      <c r="A684" s="8"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="6"/>
+      <c r="A685" s="8"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="6"/>
+      <c r="A686" s="8"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="6"/>
+      <c r="A687" s="8"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="6"/>
+      <c r="A688" s="8"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="6"/>
+      <c r="A689" s="8"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="6"/>
+      <c r="A690" s="8"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="6"/>
+      <c r="A691" s="8"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="6"/>
+      <c r="A692" s="8"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="6"/>
+      <c r="A693" s="8"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="6"/>
+      <c r="A694" s="8"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="6"/>
+      <c r="A695" s="8"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="6"/>
+      <c r="A696" s="8"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="6"/>
+      <c r="A697" s="8"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="6"/>
+      <c r="A698" s="8"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="6"/>
+      <c r="A699" s="8"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="6"/>
+      <c r="A700" s="8"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="6"/>
+      <c r="A701" s="8"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="6"/>
+      <c r="A702" s="8"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="6"/>
+      <c r="A703" s="8"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="6"/>
+      <c r="A704" s="8"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="6"/>
+      <c r="A705" s="8"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="6"/>
+      <c r="A706" s="8"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="6"/>
+      <c r="A707" s="8"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="6"/>
+      <c r="A708" s="8"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="6"/>
+      <c r="A709" s="8"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="6"/>
+      <c r="A710" s="8"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="6"/>
+      <c r="A711" s="8"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="6"/>
+      <c r="A712" s="8"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="6"/>
+      <c r="A713" s="8"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="6"/>
+      <c r="A714" s="8"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="6"/>
+      <c r="A715" s="8"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="6"/>
+      <c r="A716" s="8"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="6"/>
+      <c r="A717" s="8"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="6"/>
+      <c r="A718" s="8"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="6"/>
+      <c r="A719" s="8"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="6"/>
+      <c r="A720" s="8"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="6"/>
+      <c r="A721" s="8"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="6"/>
+      <c r="A722" s="8"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="6"/>
+      <c r="A723" s="8"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="6"/>
+      <c r="A724" s="8"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="6"/>
+      <c r="A725" s="8"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="6"/>
+      <c r="A726" s="8"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="6"/>
+      <c r="A727" s="8"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="6"/>
+      <c r="A728" s="8"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="6"/>
+      <c r="A729" s="8"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="6"/>
+      <c r="A730" s="8"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="6"/>
+      <c r="A731" s="8"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="6"/>
+      <c r="A732" s="8"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="6"/>
+      <c r="A733" s="8"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="6"/>
+      <c r="A734" s="8"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="6"/>
+      <c r="A735" s="8"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="6"/>
+      <c r="A736" s="8"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="6"/>
+      <c r="A737" s="8"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="6"/>
+      <c r="A738" s="8"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="6"/>
+      <c r="A739" s="8"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="6"/>
+      <c r="A740" s="8"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="6"/>
+      <c r="A741" s="8"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="6"/>
+      <c r="A742" s="8"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="6"/>
+      <c r="A743" s="8"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="6"/>
+      <c r="A744" s="8"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="6"/>
+      <c r="A745" s="8"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="6"/>
+      <c r="A746" s="8"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="6"/>
+      <c r="A747" s="8"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="6"/>
+      <c r="A748" s="8"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="6"/>
+      <c r="A749" s="8"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="6"/>
+      <c r="A750" s="8"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="6"/>
+      <c r="A751" s="8"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="6"/>
+      <c r="A752" s="8"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="6"/>
+      <c r="A753" s="8"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="6"/>
+      <c r="A754" s="8"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="6"/>
+      <c r="A755" s="8"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="6"/>
+      <c r="A756" s="8"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="6"/>
+      <c r="A757" s="8"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="6"/>
+      <c r="A758" s="8"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="6"/>
+      <c r="A759" s="8"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="6"/>
+      <c r="A760" s="8"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="6"/>
+      <c r="A761" s="8"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="6"/>
+      <c r="A762" s="8"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="6"/>
+      <c r="A763" s="8"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="6"/>
+      <c r="A764" s="8"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="6"/>
+      <c r="A765" s="8"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="6"/>
+      <c r="A766" s="8"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="6"/>
+      <c r="A767" s="8"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="6"/>
+      <c r="A768" s="8"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="6"/>
+      <c r="A769" s="8"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="6"/>
+      <c r="A770" s="8"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="6"/>
+      <c r="A771" s="8"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="6"/>
+      <c r="A772" s="8"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="6"/>
+      <c r="A773" s="8"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="6"/>
+      <c r="A774" s="8"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="6"/>
+      <c r="A775" s="8"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="6"/>
+      <c r="A776" s="8"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="6"/>
+      <c r="A777" s="8"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="6"/>
+      <c r="A778" s="8"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="6"/>
+      <c r="A779" s="8"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="6"/>
+      <c r="A780" s="8"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="6"/>
+      <c r="A781" s="8"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="6"/>
+      <c r="A782" s="8"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="6"/>
+      <c r="A783" s="8"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="6"/>
+      <c r="A784" s="8"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="6"/>
+      <c r="A785" s="8"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="6"/>
+      <c r="A786" s="8"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="6"/>
+      <c r="A787" s="8"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="6"/>
+      <c r="A788" s="8"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="6"/>
+      <c r="A789" s="8"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="6"/>
+      <c r="A790" s="8"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="6"/>
+      <c r="A791" s="8"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="6"/>
+      <c r="A792" s="8"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="6"/>
+      <c r="A793" s="8"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="6"/>
+      <c r="A794" s="8"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="6"/>
+      <c r="A795" s="8"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="6"/>
+      <c r="A796" s="8"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="6"/>
+      <c r="A797" s="8"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="6"/>
+      <c r="A798" s="8"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="6"/>
+      <c r="A799" s="8"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="6"/>
+      <c r="A800" s="8"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="6"/>
+      <c r="A801" s="8"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="6"/>
+      <c r="A802" s="8"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="6"/>
+      <c r="A803" s="8"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="6"/>
+      <c r="A804" s="8"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="6"/>
+      <c r="A805" s="8"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="6"/>
+      <c r="A806" s="8"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="6"/>
+      <c r="A807" s="8"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="6"/>
+      <c r="A808" s="8"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="6"/>
+      <c r="A809" s="8"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="6"/>
+      <c r="A810" s="8"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="6"/>
+      <c r="A811" s="8"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="6"/>
+      <c r="A812" s="8"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="6"/>
+      <c r="A813" s="8"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="6"/>
+      <c r="A814" s="8"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="6"/>
+      <c r="A815" s="8"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="6"/>
+      <c r="A816" s="8"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="6"/>
+      <c r="A817" s="8"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="6"/>
+      <c r="A818" s="8"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="6"/>
+      <c r="A819" s="8"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="6"/>
+      <c r="A820" s="8"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="6"/>
+      <c r="A821" s="8"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="6"/>
+      <c r="A822" s="8"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="6"/>
+      <c r="A823" s="8"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="6"/>
+      <c r="A824" s="8"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="6"/>
+      <c r="A825" s="8"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="6"/>
+      <c r="A826" s="8"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="6"/>
+      <c r="A827" s="8"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="6"/>
+      <c r="A828" s="8"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="6"/>
+      <c r="A829" s="8"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="6"/>
+      <c r="A830" s="8"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="6"/>
+      <c r="A831" s="8"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="6"/>
+      <c r="A832" s="8"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="6"/>
+      <c r="A833" s="8"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="6"/>
+      <c r="A834" s="8"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="6"/>
+      <c r="A835" s="8"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="6"/>
+      <c r="A836" s="8"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="6"/>
+      <c r="A837" s="8"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="6"/>
+      <c r="A838" s="8"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="6"/>
+      <c r="A839" s="8"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="6"/>
+      <c r="A840" s="8"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="6"/>
+      <c r="A841" s="8"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="6"/>
+      <c r="A842" s="8"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="6"/>
+      <c r="A843" s="8"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="6"/>
+      <c r="A844" s="8"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="6"/>
+      <c r="A845" s="8"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="6"/>
+      <c r="A846" s="8"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="6"/>
+      <c r="A847" s="8"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="6"/>
+      <c r="A848" s="8"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="6"/>
+      <c r="A849" s="8"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="6"/>
+      <c r="A850" s="8"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="6"/>
+      <c r="A851" s="8"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="6"/>
+      <c r="A852" s="8"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="6"/>
+      <c r="A853" s="8"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="6"/>
+      <c r="A854" s="8"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="6"/>
+      <c r="A855" s="8"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="6"/>
+      <c r="A856" s="8"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="6"/>
+      <c r="A857" s="8"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="6"/>
+      <c r="A858" s="8"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="6"/>
+      <c r="A859" s="8"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="6"/>
+      <c r="A860" s="8"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="6"/>
+      <c r="A861" s="8"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="6"/>
+      <c r="A862" s="8"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="6"/>
+      <c r="A863" s="8"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="6"/>
+      <c r="A864" s="8"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="6"/>
+      <c r="A865" s="8"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="6"/>
+      <c r="A866" s="8"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="6"/>
+      <c r="A867" s="8"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="6"/>
+      <c r="A868" s="8"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="6"/>
+      <c r="A869" s="8"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="6"/>
+      <c r="A870" s="8"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="6"/>
+      <c r="A871" s="8"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="6"/>
+      <c r="A872" s="8"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="6"/>
+      <c r="A873" s="8"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="6"/>
+      <c r="A874" s="8"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="6"/>
+      <c r="A875" s="8"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="6"/>
+      <c r="A876" s="8"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="6"/>
+      <c r="A877" s="8"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="6"/>
+      <c r="A878" s="8"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="6"/>
+      <c r="A879" s="8"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="6"/>
+      <c r="A880" s="8"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="6"/>
+      <c r="A881" s="8"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="6"/>
+      <c r="A882" s="8"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="6"/>
+      <c r="A883" s="8"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="6"/>
+      <c r="A884" s="8"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="6"/>
+      <c r="A885" s="8"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="6"/>
+      <c r="A886" s="8"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="6"/>
+      <c r="A887" s="8"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="6"/>
+      <c r="A888" s="8"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="6"/>
+      <c r="A889" s="8"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="6"/>
+      <c r="A890" s="8"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="6"/>
+      <c r="A891" s="8"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="6"/>
+      <c r="A892" s="8"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="6"/>
+      <c r="A893" s="8"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="6"/>
+      <c r="A894" s="8"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="6"/>
+      <c r="A895" s="8"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="6"/>
+      <c r="A896" s="8"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="6"/>
+      <c r="A897" s="8"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="6"/>
+      <c r="A898" s="8"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="6"/>
+      <c r="A899" s="8"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="6"/>
+      <c r="A900" s="8"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="6"/>
+      <c r="A901" s="8"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="6"/>
+      <c r="A902" s="8"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="6"/>
+      <c r="A903" s="8"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="6"/>
+      <c r="A904" s="8"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="6"/>
+      <c r="A905" s="8"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="6"/>
+      <c r="A906" s="8"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="6"/>
+      <c r="A907" s="8"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="6"/>
+      <c r="A908" s="8"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="6"/>
+      <c r="A909" s="8"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="6"/>
+      <c r="A910" s="8"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="6"/>
+      <c r="A911" s="8"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="6"/>
+      <c r="A912" s="8"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="6"/>
+      <c r="A913" s="8"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="6"/>
+      <c r="A914" s="8"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="6"/>
+      <c r="A915" s="8"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="6"/>
+      <c r="A916" s="8"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="6"/>
+      <c r="A917" s="8"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="6"/>
+      <c r="A918" s="8"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="6"/>
+      <c r="A919" s="8"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="6"/>
+      <c r="A920" s="8"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="6"/>
+      <c r="A921" s="8"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="6"/>
+      <c r="A922" s="8"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="6"/>
+      <c r="A923" s="8"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="6"/>
+      <c r="A924" s="8"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="6"/>
+      <c r="A925" s="8"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="6"/>
+      <c r="A926" s="8"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="6"/>
+      <c r="A927" s="8"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="6"/>
+      <c r="A928" s="8"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="6"/>
+      <c r="A929" s="8"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="6"/>
+      <c r="A930" s="8"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="6"/>
+      <c r="A931" s="8"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="6"/>
+      <c r="A932" s="8"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="6"/>
+      <c r="A933" s="8"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="6"/>
+      <c r="A934" s="8"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="6"/>
+      <c r="A935" s="8"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="6"/>
+      <c r="A936" s="8"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="6"/>
+      <c r="A937" s="8"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="6"/>
+      <c r="A938" s="8"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="6"/>
+      <c r="A939" s="8"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="6"/>
+      <c r="A940" s="8"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="6"/>
+      <c r="A941" s="8"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="6"/>
+      <c r="A942" s="8"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="6"/>
+      <c r="A943" s="8"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="6"/>
+      <c r="A944" s="8"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="6"/>
+      <c r="A945" s="8"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="6"/>
+      <c r="A946" s="8"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="6"/>
+      <c r="A947" s="8"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="6"/>
+      <c r="A948" s="8"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="6"/>
+      <c r="A949" s="8"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="6"/>
+      <c r="A950" s="8"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="6"/>
+      <c r="A951" s="8"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="6"/>
+      <c r="A952" s="8"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="6"/>
+      <c r="A953" s="8"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="6"/>
+      <c r="A954" s="8"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="6"/>
+      <c r="A955" s="8"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="6"/>
+      <c r="A956" s="8"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="6"/>
+      <c r="A957" s="8"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="6"/>
+      <c r="A958" s="8"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="6"/>
+      <c r="A959" s="8"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="6"/>
+      <c r="A960" s="8"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="6"/>
+      <c r="A961" s="8"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="6"/>
+      <c r="A962" s="8"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="6"/>
+      <c r="A963" s="8"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="6"/>
+      <c r="A964" s="8"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="6"/>
+      <c r="A965" s="8"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="6"/>
+      <c r="A966" s="8"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="6"/>
+      <c r="A967" s="8"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="6"/>
+      <c r="A968" s="8"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="6"/>
+      <c r="A969" s="8"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="6"/>
+      <c r="A970" s="8"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="6"/>
+      <c r="A971" s="8"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="6"/>
+      <c r="A972" s="8"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="6"/>
+      <c r="A973" s="8"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="6"/>
+      <c r="A974" s="8"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="6"/>
+      <c r="A975" s="8"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="6"/>
+      <c r="A976" s="8"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="6"/>
+      <c r="A977" s="8"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="6"/>
+      <c r="A978" s="8"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="6"/>
+      <c r="A979" s="8"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="6"/>
+      <c r="A980" s="8"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="6"/>
+      <c r="A981" s="8"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="6"/>
+      <c r="A982" s="8"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="6"/>
+      <c r="A983" s="8"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="6"/>
+      <c r="A984" s="8"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="6"/>
+      <c r="A985" s="8"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="6"/>
+      <c r="A986" s="8"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="6"/>
+      <c r="A987" s="8"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="6"/>
+      <c r="A988" s="8"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="6"/>
+      <c r="A989" s="8"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="6"/>
+      <c r="A990" s="8"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="6"/>
+      <c r="A991" s="8"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="6"/>
+      <c r="A992" s="8"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="6"/>
+      <c r="A993" s="8"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="6"/>
+      <c r="A994" s="8"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="6"/>
+      <c r="A995" s="8"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="6"/>
+      <c r="A996" s="8"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="6"/>
+      <c r="A997" s="8"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="6"/>
+      <c r="A998" s="8"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="6"/>
+      <c r="A999" s="8"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="6"/>
+      <c r="A1000" s="8"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1">
-      <c r="A1001" s="6"/>
+      <c r="A1001" s="8"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1">
-      <c r="A1002" s="6"/>
+      <c r="A1002" s="8"/>
     </row>
   </sheetData>
   <dataValidations>
@@ -4935,2344 +4942,2344 @@
       <c r="A220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="6"/>
+      <c r="A221" s="8"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="6"/>
+      <c r="A222" s="8"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="6"/>
+      <c r="A223" s="8"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="6"/>
+      <c r="A224" s="8"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="6"/>
+      <c r="A225" s="8"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="6"/>
+      <c r="A226" s="8"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="6"/>
+      <c r="A227" s="8"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="6"/>
+      <c r="A228" s="8"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="6"/>
+      <c r="A229" s="8"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="6"/>
+      <c r="A230" s="8"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="6"/>
+      <c r="A231" s="8"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="6"/>
+      <c r="A232" s="8"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="6"/>
+      <c r="A233" s="8"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="6"/>
+      <c r="A234" s="8"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="6"/>
+      <c r="A235" s="8"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="6"/>
+      <c r="A236" s="8"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="6"/>
+      <c r="A237" s="8"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="6"/>
+      <c r="A238" s="8"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="6"/>
+      <c r="A239" s="8"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="6"/>
+      <c r="A240" s="8"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="6"/>
+      <c r="A241" s="8"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="6"/>
+      <c r="A242" s="8"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="6"/>
+      <c r="A243" s="8"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="6"/>
+      <c r="A244" s="8"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="6"/>
+      <c r="A245" s="8"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="6"/>
+      <c r="A246" s="8"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="6"/>
+      <c r="A247" s="8"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="6"/>
+      <c r="A248" s="8"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="6"/>
+      <c r="A249" s="8"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="6"/>
+      <c r="A250" s="8"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="6"/>
+      <c r="A251" s="8"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="6"/>
+      <c r="A252" s="8"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="6"/>
+      <c r="A253" s="8"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="6"/>
+      <c r="A254" s="8"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="6"/>
+      <c r="A255" s="8"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="6"/>
+      <c r="A256" s="8"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="6"/>
+      <c r="A257" s="8"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="6"/>
+      <c r="A258" s="8"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="6"/>
+      <c r="A259" s="8"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="6"/>
+      <c r="A260" s="8"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="6"/>
+      <c r="A261" s="8"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="6"/>
+      <c r="A262" s="8"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="6"/>
+      <c r="A263" s="8"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="6"/>
+      <c r="A264" s="8"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="6"/>
+      <c r="A265" s="8"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="6"/>
+      <c r="A266" s="8"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="6"/>
+      <c r="A267" s="8"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="6"/>
+      <c r="A268" s="8"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="6"/>
+      <c r="A269" s="8"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="6"/>
+      <c r="A270" s="8"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="6"/>
+      <c r="A271" s="8"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="6"/>
+      <c r="A272" s="8"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="6"/>
+      <c r="A273" s="8"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="6"/>
+      <c r="A274" s="8"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="6"/>
+      <c r="A275" s="8"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="6"/>
+      <c r="A276" s="8"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="6"/>
+      <c r="A277" s="8"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="6"/>
+      <c r="A278" s="8"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="6"/>
+      <c r="A279" s="8"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="6"/>
+      <c r="A280" s="8"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="6"/>
+      <c r="A281" s="8"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="6"/>
+      <c r="A282" s="8"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="6"/>
+      <c r="A283" s="8"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="6"/>
+      <c r="A284" s="8"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="6"/>
+      <c r="A285" s="8"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="6"/>
+      <c r="A286" s="8"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="6"/>
+      <c r="A287" s="8"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="6"/>
+      <c r="A288" s="8"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="6"/>
+      <c r="A289" s="8"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="6"/>
+      <c r="A290" s="8"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="6"/>
+      <c r="A291" s="8"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="6"/>
+      <c r="A292" s="8"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="6"/>
+      <c r="A293" s="8"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="6"/>
+      <c r="A294" s="8"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="6"/>
+      <c r="A295" s="8"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="6"/>
+      <c r="A296" s="8"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="6"/>
+      <c r="A297" s="8"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="6"/>
+      <c r="A298" s="8"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="6"/>
+      <c r="A299" s="8"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="6"/>
+      <c r="A300" s="8"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="6"/>
+      <c r="A301" s="8"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="6"/>
+      <c r="A302" s="8"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="6"/>
+      <c r="A303" s="8"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="6"/>
+      <c r="A304" s="8"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="6"/>
+      <c r="A305" s="8"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="6"/>
+      <c r="A306" s="8"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="6"/>
+      <c r="A307" s="8"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="6"/>
+      <c r="A308" s="8"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="6"/>
+      <c r="A309" s="8"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="6"/>
+      <c r="A310" s="8"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="6"/>
+      <c r="A311" s="8"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="6"/>
+      <c r="A312" s="8"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="6"/>
+      <c r="A313" s="8"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="6"/>
+      <c r="A314" s="8"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="6"/>
+      <c r="A315" s="8"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="6"/>
+      <c r="A316" s="8"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="6"/>
+      <c r="A317" s="8"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="6"/>
+      <c r="A318" s="8"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="6"/>
+      <c r="A319" s="8"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="6"/>
+      <c r="A320" s="8"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="6"/>
+      <c r="A321" s="8"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="6"/>
+      <c r="A322" s="8"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="6"/>
+      <c r="A323" s="8"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="6"/>
+      <c r="A324" s="8"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="6"/>
+      <c r="A325" s="8"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="6"/>
+      <c r="A326" s="8"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="6"/>
+      <c r="A327" s="8"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="6"/>
+      <c r="A328" s="8"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="6"/>
+      <c r="A329" s="8"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="6"/>
+      <c r="A330" s="8"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="6"/>
+      <c r="A331" s="8"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="6"/>
+      <c r="A332" s="8"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="6"/>
+      <c r="A333" s="8"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="6"/>
+      <c r="A334" s="8"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="6"/>
+      <c r="A335" s="8"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="6"/>
+      <c r="A336" s="8"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="6"/>
+      <c r="A337" s="8"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="6"/>
+      <c r="A338" s="8"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="6"/>
+      <c r="A339" s="8"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="6"/>
+      <c r="A340" s="8"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="6"/>
+      <c r="A341" s="8"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="6"/>
+      <c r="A342" s="8"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="6"/>
+      <c r="A343" s="8"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="6"/>
+      <c r="A344" s="8"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="6"/>
+      <c r="A345" s="8"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="6"/>
+      <c r="A346" s="8"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="6"/>
+      <c r="A347" s="8"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="6"/>
+      <c r="A348" s="8"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="6"/>
+      <c r="A349" s="8"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="6"/>
+      <c r="A350" s="8"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="6"/>
+      <c r="A351" s="8"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="6"/>
+      <c r="A352" s="8"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="6"/>
+      <c r="A353" s="8"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="6"/>
+      <c r="A354" s="8"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="6"/>
+      <c r="A355" s="8"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="6"/>
+      <c r="A356" s="8"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="6"/>
+      <c r="A357" s="8"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="6"/>
+      <c r="A358" s="8"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="6"/>
+      <c r="A359" s="8"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="6"/>
+      <c r="A360" s="8"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="6"/>
+      <c r="A361" s="8"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="6"/>
+      <c r="A362" s="8"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="6"/>
+      <c r="A363" s="8"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="6"/>
+      <c r="A364" s="8"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="6"/>
+      <c r="A365" s="8"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="6"/>
+      <c r="A366" s="8"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="6"/>
+      <c r="A367" s="8"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="6"/>
+      <c r="A368" s="8"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="6"/>
+      <c r="A369" s="8"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="6"/>
+      <c r="A370" s="8"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="6"/>
+      <c r="A371" s="8"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="6"/>
+      <c r="A372" s="8"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="6"/>
+      <c r="A373" s="8"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="6"/>
+      <c r="A374" s="8"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="6"/>
+      <c r="A375" s="8"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="6"/>
+      <c r="A376" s="8"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="6"/>
+      <c r="A377" s="8"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="6"/>
+      <c r="A378" s="8"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="6"/>
+      <c r="A379" s="8"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="6"/>
+      <c r="A380" s="8"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="6"/>
+      <c r="A381" s="8"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="6"/>
+      <c r="A382" s="8"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="6"/>
+      <c r="A383" s="8"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="6"/>
+      <c r="A384" s="8"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="6"/>
+      <c r="A385" s="8"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="6"/>
+      <c r="A386" s="8"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="6"/>
+      <c r="A387" s="8"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="6"/>
+      <c r="A388" s="8"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="6"/>
+      <c r="A389" s="8"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="6"/>
+      <c r="A390" s="8"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="6"/>
+      <c r="A391" s="8"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="6"/>
+      <c r="A392" s="8"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="6"/>
+      <c r="A393" s="8"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="6"/>
+      <c r="A394" s="8"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="6"/>
+      <c r="A395" s="8"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="6"/>
+      <c r="A396" s="8"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="6"/>
+      <c r="A397" s="8"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="6"/>
+      <c r="A398" s="8"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="6"/>
+      <c r="A399" s="8"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="6"/>
+      <c r="A400" s="8"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="6"/>
+      <c r="A401" s="8"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="6"/>
+      <c r="A402" s="8"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="6"/>
+      <c r="A403" s="8"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="6"/>
+      <c r="A404" s="8"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="6"/>
+      <c r="A405" s="8"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="6"/>
+      <c r="A406" s="8"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="6"/>
+      <c r="A407" s="8"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="6"/>
+      <c r="A408" s="8"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="6"/>
+      <c r="A409" s="8"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="6"/>
+      <c r="A410" s="8"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="6"/>
+      <c r="A411" s="8"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="6"/>
+      <c r="A412" s="8"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="6"/>
+      <c r="A413" s="8"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="6"/>
+      <c r="A414" s="8"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="6"/>
+      <c r="A415" s="8"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="6"/>
+      <c r="A416" s="8"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="6"/>
+      <c r="A417" s="8"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="6"/>
+      <c r="A418" s="8"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="6"/>
+      <c r="A419" s="8"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="6"/>
+      <c r="A420" s="8"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="6"/>
+      <c r="A421" s="8"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="6"/>
+      <c r="A422" s="8"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="6"/>
+      <c r="A423" s="8"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="6"/>
+      <c r="A424" s="8"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="6"/>
+      <c r="A425" s="8"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="6"/>
+      <c r="A426" s="8"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="6"/>
+      <c r="A427" s="8"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="6"/>
+      <c r="A428" s="8"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="6"/>
+      <c r="A429" s="8"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="6"/>
+      <c r="A430" s="8"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="6"/>
+      <c r="A431" s="8"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="6"/>
+      <c r="A432" s="8"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="6"/>
+      <c r="A433" s="8"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="6"/>
+      <c r="A434" s="8"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="6"/>
+      <c r="A435" s="8"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="6"/>
+      <c r="A436" s="8"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="6"/>
+      <c r="A437" s="8"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="6"/>
+      <c r="A438" s="8"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="6"/>
+      <c r="A439" s="8"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="6"/>
+      <c r="A440" s="8"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="6"/>
+      <c r="A441" s="8"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="6"/>
+      <c r="A442" s="8"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="6"/>
+      <c r="A443" s="8"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="6"/>
+      <c r="A444" s="8"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="6"/>
+      <c r="A445" s="8"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="6"/>
+      <c r="A446" s="8"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="6"/>
+      <c r="A447" s="8"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="6"/>
+      <c r="A448" s="8"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="6"/>
+      <c r="A449" s="8"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="6"/>
+      <c r="A450" s="8"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="6"/>
+      <c r="A451" s="8"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="6"/>
+      <c r="A452" s="8"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="6"/>
+      <c r="A453" s="8"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="6"/>
+      <c r="A454" s="8"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="6"/>
+      <c r="A455" s="8"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="6"/>
+      <c r="A456" s="8"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="6"/>
+      <c r="A457" s="8"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="6"/>
+      <c r="A458" s="8"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="6"/>
+      <c r="A459" s="8"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="6"/>
+      <c r="A460" s="8"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="6"/>
+      <c r="A461" s="8"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="6"/>
+      <c r="A462" s="8"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="6"/>
+      <c r="A463" s="8"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="6"/>
+      <c r="A464" s="8"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="6"/>
+      <c r="A465" s="8"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="6"/>
+      <c r="A466" s="8"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="6"/>
+      <c r="A467" s="8"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="6"/>
+      <c r="A468" s="8"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="6"/>
+      <c r="A469" s="8"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="6"/>
+      <c r="A470" s="8"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="6"/>
+      <c r="A471" s="8"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="6"/>
+      <c r="A472" s="8"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="6"/>
+      <c r="A473" s="8"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="6"/>
+      <c r="A474" s="8"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="6"/>
+      <c r="A475" s="8"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="6"/>
+      <c r="A476" s="8"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="6"/>
+      <c r="A477" s="8"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="6"/>
+      <c r="A478" s="8"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="6"/>
+      <c r="A479" s="8"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="6"/>
+      <c r="A480" s="8"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="6"/>
+      <c r="A481" s="8"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="6"/>
+      <c r="A482" s="8"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="6"/>
+      <c r="A483" s="8"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="6"/>
+      <c r="A484" s="8"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="6"/>
+      <c r="A485" s="8"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="6"/>
+      <c r="A486" s="8"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="6"/>
+      <c r="A487" s="8"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="6"/>
+      <c r="A488" s="8"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="6"/>
+      <c r="A489" s="8"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="6"/>
+      <c r="A490" s="8"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="6"/>
+      <c r="A491" s="8"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="6"/>
+      <c r="A492" s="8"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="6"/>
+      <c r="A493" s="8"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="6"/>
+      <c r="A494" s="8"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="6"/>
+      <c r="A495" s="8"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="6"/>
+      <c r="A496" s="8"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="6"/>
+      <c r="A497" s="8"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="6"/>
+      <c r="A498" s="8"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="6"/>
+      <c r="A499" s="8"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="6"/>
+      <c r="A500" s="8"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="6"/>
+      <c r="A501" s="8"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="6"/>
+      <c r="A502" s="8"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="6"/>
+      <c r="A503" s="8"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="6"/>
+      <c r="A504" s="8"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="6"/>
+      <c r="A505" s="8"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="6"/>
+      <c r="A506" s="8"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="6"/>
+      <c r="A507" s="8"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="6"/>
+      <c r="A508" s="8"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="6"/>
+      <c r="A509" s="8"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="6"/>
+      <c r="A510" s="8"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="6"/>
+      <c r="A511" s="8"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="6"/>
+      <c r="A512" s="8"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="6"/>
+      <c r="A513" s="8"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="6"/>
+      <c r="A514" s="8"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="6"/>
+      <c r="A515" s="8"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="6"/>
+      <c r="A516" s="8"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="6"/>
+      <c r="A517" s="8"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="6"/>
+      <c r="A518" s="8"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="6"/>
+      <c r="A519" s="8"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="6"/>
+      <c r="A520" s="8"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="6"/>
+      <c r="A521" s="8"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="6"/>
+      <c r="A522" s="8"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="6"/>
+      <c r="A523" s="8"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="6"/>
+      <c r="A524" s="8"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="6"/>
+      <c r="A525" s="8"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="6"/>
+      <c r="A526" s="8"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="6"/>
+      <c r="A527" s="8"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="6"/>
+      <c r="A528" s="8"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="6"/>
+      <c r="A529" s="8"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="6"/>
+      <c r="A530" s="8"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="6"/>
+      <c r="A531" s="8"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="6"/>
+      <c r="A532" s="8"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="6"/>
+      <c r="A533" s="8"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="6"/>
+      <c r="A534" s="8"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="6"/>
+      <c r="A535" s="8"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="6"/>
+      <c r="A536" s="8"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="6"/>
+      <c r="A537" s="8"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="6"/>
+      <c r="A538" s="8"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="6"/>
+      <c r="A539" s="8"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="6"/>
+      <c r="A540" s="8"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="6"/>
+      <c r="A541" s="8"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="6"/>
+      <c r="A542" s="8"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="6"/>
+      <c r="A543" s="8"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="6"/>
+      <c r="A544" s="8"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="6"/>
+      <c r="A545" s="8"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="6"/>
+      <c r="A546" s="8"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="6"/>
+      <c r="A547" s="8"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="6"/>
+      <c r="A548" s="8"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="6"/>
+      <c r="A549" s="8"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="6"/>
+      <c r="A550" s="8"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="6"/>
+      <c r="A551" s="8"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="6"/>
+      <c r="A552" s="8"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="6"/>
+      <c r="A553" s="8"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="6"/>
+      <c r="A554" s="8"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="6"/>
+      <c r="A555" s="8"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="6"/>
+      <c r="A556" s="8"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="6"/>
+      <c r="A557" s="8"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="6"/>
+      <c r="A558" s="8"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="6"/>
+      <c r="A559" s="8"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="6"/>
+      <c r="A560" s="8"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="6"/>
+      <c r="A561" s="8"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="6"/>
+      <c r="A562" s="8"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="6"/>
+      <c r="A563" s="8"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="6"/>
+      <c r="A564" s="8"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="6"/>
+      <c r="A565" s="8"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="6"/>
+      <c r="A566" s="8"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="6"/>
+      <c r="A567" s="8"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="6"/>
+      <c r="A568" s="8"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="6"/>
+      <c r="A569" s="8"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="6"/>
+      <c r="A570" s="8"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="6"/>
+      <c r="A571" s="8"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="6"/>
+      <c r="A572" s="8"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="6"/>
+      <c r="A573" s="8"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="6"/>
+      <c r="A574" s="8"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="6"/>
+      <c r="A575" s="8"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="6"/>
+      <c r="A576" s="8"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="6"/>
+      <c r="A577" s="8"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="6"/>
+      <c r="A578" s="8"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="6"/>
+      <c r="A579" s="8"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="6"/>
+      <c r="A580" s="8"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="6"/>
+      <c r="A581" s="8"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="6"/>
+      <c r="A582" s="8"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="6"/>
+      <c r="A583" s="8"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="6"/>
+      <c r="A584" s="8"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="6"/>
+      <c r="A585" s="8"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="6"/>
+      <c r="A586" s="8"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="6"/>
+      <c r="A587" s="8"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="6"/>
+      <c r="A588" s="8"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="6"/>
+      <c r="A589" s="8"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="6"/>
+      <c r="A590" s="8"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="6"/>
+      <c r="A591" s="8"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="6"/>
+      <c r="A592" s="8"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="6"/>
+      <c r="A593" s="8"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="6"/>
+      <c r="A594" s="8"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="6"/>
+      <c r="A595" s="8"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="6"/>
+      <c r="A596" s="8"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="6"/>
+      <c r="A597" s="8"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="6"/>
+      <c r="A598" s="8"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="6"/>
+      <c r="A599" s="8"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="6"/>
+      <c r="A600" s="8"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="6"/>
+      <c r="A601" s="8"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="6"/>
+      <c r="A602" s="8"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="6"/>
+      <c r="A603" s="8"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="6"/>
+      <c r="A604" s="8"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="6"/>
+      <c r="A605" s="8"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="6"/>
+      <c r="A606" s="8"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="6"/>
+      <c r="A607" s="8"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="6"/>
+      <c r="A608" s="8"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="6"/>
+      <c r="A609" s="8"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="6"/>
+      <c r="A610" s="8"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="6"/>
+      <c r="A611" s="8"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="6"/>
+      <c r="A612" s="8"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="6"/>
+      <c r="A613" s="8"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="6"/>
+      <c r="A614" s="8"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="6"/>
+      <c r="A615" s="8"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="6"/>
+      <c r="A616" s="8"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="6"/>
+      <c r="A617" s="8"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="6"/>
+      <c r="A618" s="8"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="6"/>
+      <c r="A619" s="8"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="6"/>
+      <c r="A620" s="8"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="6"/>
+      <c r="A621" s="8"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="6"/>
+      <c r="A622" s="8"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="6"/>
+      <c r="A623" s="8"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="6"/>
+      <c r="A624" s="8"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="6"/>
+      <c r="A625" s="8"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="6"/>
+      <c r="A626" s="8"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="6"/>
+      <c r="A627" s="8"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="6"/>
+      <c r="A628" s="8"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="6"/>
+      <c r="A629" s="8"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="6"/>
+      <c r="A630" s="8"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="6"/>
+      <c r="A631" s="8"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="6"/>
+      <c r="A632" s="8"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="6"/>
+      <c r="A633" s="8"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="6"/>
+      <c r="A634" s="8"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="6"/>
+      <c r="A635" s="8"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="6"/>
+      <c r="A636" s="8"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="6"/>
+      <c r="A637" s="8"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="6"/>
+      <c r="A638" s="8"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="6"/>
+      <c r="A639" s="8"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="6"/>
+      <c r="A640" s="8"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="6"/>
+      <c r="A641" s="8"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="6"/>
+      <c r="A642" s="8"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="6"/>
+      <c r="A643" s="8"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="6"/>
+      <c r="A644" s="8"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="6"/>
+      <c r="A645" s="8"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="6"/>
+      <c r="A646" s="8"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="6"/>
+      <c r="A647" s="8"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="6"/>
+      <c r="A648" s="8"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="6"/>
+      <c r="A649" s="8"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="6"/>
+      <c r="A650" s="8"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="6"/>
+      <c r="A651" s="8"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="6"/>
+      <c r="A652" s="8"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="6"/>
+      <c r="A653" s="8"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="6"/>
+      <c r="A654" s="8"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="6"/>
+      <c r="A655" s="8"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="6"/>
+      <c r="A656" s="8"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="6"/>
+      <c r="A657" s="8"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="6"/>
+      <c r="A658" s="8"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="6"/>
+      <c r="A659" s="8"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="6"/>
+      <c r="A660" s="8"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="6"/>
+      <c r="A661" s="8"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="6"/>
+      <c r="A662" s="8"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="6"/>
+      <c r="A663" s="8"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="6"/>
+      <c r="A664" s="8"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="6"/>
+      <c r="A665" s="8"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="6"/>
+      <c r="A666" s="8"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="6"/>
+      <c r="A667" s="8"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="6"/>
+      <c r="A668" s="8"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="6"/>
+      <c r="A669" s="8"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="6"/>
+      <c r="A670" s="8"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="6"/>
+      <c r="A671" s="8"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="6"/>
+      <c r="A672" s="8"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="6"/>
+      <c r="A673" s="8"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="6"/>
+      <c r="A674" s="8"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="6"/>
+      <c r="A675" s="8"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="6"/>
+      <c r="A676" s="8"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="6"/>
+      <c r="A677" s="8"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="6"/>
+      <c r="A678" s="8"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="6"/>
+      <c r="A679" s="8"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="6"/>
+      <c r="A680" s="8"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="6"/>
+      <c r="A681" s="8"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="6"/>
+      <c r="A682" s="8"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="6"/>
+      <c r="A683" s="8"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="6"/>
+      <c r="A684" s="8"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="6"/>
+      <c r="A685" s="8"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="6"/>
+      <c r="A686" s="8"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="6"/>
+      <c r="A687" s="8"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="6"/>
+      <c r="A688" s="8"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="6"/>
+      <c r="A689" s="8"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="6"/>
+      <c r="A690" s="8"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="6"/>
+      <c r="A691" s="8"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="6"/>
+      <c r="A692" s="8"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="6"/>
+      <c r="A693" s="8"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="6"/>
+      <c r="A694" s="8"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="6"/>
+      <c r="A695" s="8"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="6"/>
+      <c r="A696" s="8"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="6"/>
+      <c r="A697" s="8"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="6"/>
+      <c r="A698" s="8"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="6"/>
+      <c r="A699" s="8"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="6"/>
+      <c r="A700" s="8"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="6"/>
+      <c r="A701" s="8"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="6"/>
+      <c r="A702" s="8"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="6"/>
+      <c r="A703" s="8"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="6"/>
+      <c r="A704" s="8"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="6"/>
+      <c r="A705" s="8"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="6"/>
+      <c r="A706" s="8"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="6"/>
+      <c r="A707" s="8"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="6"/>
+      <c r="A708" s="8"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="6"/>
+      <c r="A709" s="8"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="6"/>
+      <c r="A710" s="8"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="6"/>
+      <c r="A711" s="8"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="6"/>
+      <c r="A712" s="8"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="6"/>
+      <c r="A713" s="8"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="6"/>
+      <c r="A714" s="8"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="6"/>
+      <c r="A715" s="8"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="6"/>
+      <c r="A716" s="8"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="6"/>
+      <c r="A717" s="8"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="6"/>
+      <c r="A718" s="8"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="6"/>
+      <c r="A719" s="8"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="6"/>
+      <c r="A720" s="8"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="6"/>
+      <c r="A721" s="8"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="6"/>
+      <c r="A722" s="8"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="6"/>
+      <c r="A723" s="8"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="6"/>
+      <c r="A724" s="8"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="6"/>
+      <c r="A725" s="8"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="6"/>
+      <c r="A726" s="8"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="6"/>
+      <c r="A727" s="8"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="6"/>
+      <c r="A728" s="8"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="6"/>
+      <c r="A729" s="8"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="6"/>
+      <c r="A730" s="8"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="6"/>
+      <c r="A731" s="8"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="6"/>
+      <c r="A732" s="8"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="6"/>
+      <c r="A733" s="8"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="6"/>
+      <c r="A734" s="8"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="6"/>
+      <c r="A735" s="8"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="6"/>
+      <c r="A736" s="8"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="6"/>
+      <c r="A737" s="8"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="6"/>
+      <c r="A738" s="8"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="6"/>
+      <c r="A739" s="8"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="6"/>
+      <c r="A740" s="8"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="6"/>
+      <c r="A741" s="8"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="6"/>
+      <c r="A742" s="8"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="6"/>
+      <c r="A743" s="8"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="6"/>
+      <c r="A744" s="8"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="6"/>
+      <c r="A745" s="8"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="6"/>
+      <c r="A746" s="8"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="6"/>
+      <c r="A747" s="8"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="6"/>
+      <c r="A748" s="8"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="6"/>
+      <c r="A749" s="8"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="6"/>
+      <c r="A750" s="8"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="6"/>
+      <c r="A751" s="8"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="6"/>
+      <c r="A752" s="8"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="6"/>
+      <c r="A753" s="8"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="6"/>
+      <c r="A754" s="8"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="6"/>
+      <c r="A755" s="8"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="6"/>
+      <c r="A756" s="8"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="6"/>
+      <c r="A757" s="8"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="6"/>
+      <c r="A758" s="8"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="6"/>
+      <c r="A759" s="8"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="6"/>
+      <c r="A760" s="8"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="6"/>
+      <c r="A761" s="8"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="6"/>
+      <c r="A762" s="8"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="6"/>
+      <c r="A763" s="8"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="6"/>
+      <c r="A764" s="8"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="6"/>
+      <c r="A765" s="8"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="6"/>
+      <c r="A766" s="8"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="6"/>
+      <c r="A767" s="8"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="6"/>
+      <c r="A768" s="8"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="6"/>
+      <c r="A769" s="8"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="6"/>
+      <c r="A770" s="8"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="6"/>
+      <c r="A771" s="8"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="6"/>
+      <c r="A772" s="8"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="6"/>
+      <c r="A773" s="8"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="6"/>
+      <c r="A774" s="8"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="6"/>
+      <c r="A775" s="8"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="6"/>
+      <c r="A776" s="8"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="6"/>
+      <c r="A777" s="8"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="6"/>
+      <c r="A778" s="8"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="6"/>
+      <c r="A779" s="8"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="6"/>
+      <c r="A780" s="8"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="6"/>
+      <c r="A781" s="8"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="6"/>
+      <c r="A782" s="8"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="6"/>
+      <c r="A783" s="8"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="6"/>
+      <c r="A784" s="8"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="6"/>
+      <c r="A785" s="8"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="6"/>
+      <c r="A786" s="8"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="6"/>
+      <c r="A787" s="8"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="6"/>
+      <c r="A788" s="8"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="6"/>
+      <c r="A789" s="8"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="6"/>
+      <c r="A790" s="8"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="6"/>
+      <c r="A791" s="8"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="6"/>
+      <c r="A792" s="8"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="6"/>
+      <c r="A793" s="8"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="6"/>
+      <c r="A794" s="8"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="6"/>
+      <c r="A795" s="8"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="6"/>
+      <c r="A796" s="8"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="6"/>
+      <c r="A797" s="8"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="6"/>
+      <c r="A798" s="8"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="6"/>
+      <c r="A799" s="8"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="6"/>
+      <c r="A800" s="8"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="6"/>
+      <c r="A801" s="8"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="6"/>
+      <c r="A802" s="8"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="6"/>
+      <c r="A803" s="8"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="6"/>
+      <c r="A804" s="8"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="6"/>
+      <c r="A805" s="8"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="6"/>
+      <c r="A806" s="8"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="6"/>
+      <c r="A807" s="8"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="6"/>
+      <c r="A808" s="8"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="6"/>
+      <c r="A809" s="8"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="6"/>
+      <c r="A810" s="8"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="6"/>
+      <c r="A811" s="8"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="6"/>
+      <c r="A812" s="8"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="6"/>
+      <c r="A813" s="8"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="6"/>
+      <c r="A814" s="8"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="6"/>
+      <c r="A815" s="8"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="6"/>
+      <c r="A816" s="8"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="6"/>
+      <c r="A817" s="8"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="6"/>
+      <c r="A818" s="8"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="6"/>
+      <c r="A819" s="8"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="6"/>
+      <c r="A820" s="8"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="6"/>
+      <c r="A821" s="8"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="6"/>
+      <c r="A822" s="8"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="6"/>
+      <c r="A823" s="8"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="6"/>
+      <c r="A824" s="8"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="6"/>
+      <c r="A825" s="8"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="6"/>
+      <c r="A826" s="8"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="6"/>
+      <c r="A827" s="8"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="6"/>
+      <c r="A828" s="8"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="6"/>
+      <c r="A829" s="8"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="6"/>
+      <c r="A830" s="8"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="6"/>
+      <c r="A831" s="8"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="6"/>
+      <c r="A832" s="8"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="6"/>
+      <c r="A833" s="8"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="6"/>
+      <c r="A834" s="8"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="6"/>
+      <c r="A835" s="8"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="6"/>
+      <c r="A836" s="8"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="6"/>
+      <c r="A837" s="8"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="6"/>
+      <c r="A838" s="8"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="6"/>
+      <c r="A839" s="8"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="6"/>
+      <c r="A840" s="8"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="6"/>
+      <c r="A841" s="8"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="6"/>
+      <c r="A842" s="8"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="6"/>
+      <c r="A843" s="8"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="6"/>
+      <c r="A844" s="8"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="6"/>
+      <c r="A845" s="8"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="6"/>
+      <c r="A846" s="8"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="6"/>
+      <c r="A847" s="8"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="6"/>
+      <c r="A848" s="8"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="6"/>
+      <c r="A849" s="8"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="6"/>
+      <c r="A850" s="8"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="6"/>
+      <c r="A851" s="8"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="6"/>
+      <c r="A852" s="8"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="6"/>
+      <c r="A853" s="8"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="6"/>
+      <c r="A854" s="8"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="6"/>
+      <c r="A855" s="8"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="6"/>
+      <c r="A856" s="8"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="6"/>
+      <c r="A857" s="8"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="6"/>
+      <c r="A858" s="8"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="6"/>
+      <c r="A859" s="8"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="6"/>
+      <c r="A860" s="8"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="6"/>
+      <c r="A861" s="8"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="6"/>
+      <c r="A862" s="8"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="6"/>
+      <c r="A863" s="8"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="6"/>
+      <c r="A864" s="8"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="6"/>
+      <c r="A865" s="8"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="6"/>
+      <c r="A866" s="8"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="6"/>
+      <c r="A867" s="8"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="6"/>
+      <c r="A868" s="8"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="6"/>
+      <c r="A869" s="8"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="6"/>
+      <c r="A870" s="8"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="6"/>
+      <c r="A871" s="8"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="6"/>
+      <c r="A872" s="8"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="6"/>
+      <c r="A873" s="8"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="6"/>
+      <c r="A874" s="8"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="6"/>
+      <c r="A875" s="8"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="6"/>
+      <c r="A876" s="8"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="6"/>
+      <c r="A877" s="8"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="6"/>
+      <c r="A878" s="8"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="6"/>
+      <c r="A879" s="8"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="6"/>
+      <c r="A880" s="8"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="6"/>
+      <c r="A881" s="8"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="6"/>
+      <c r="A882" s="8"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="6"/>
+      <c r="A883" s="8"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="6"/>
+      <c r="A884" s="8"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="6"/>
+      <c r="A885" s="8"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="6"/>
+      <c r="A886" s="8"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="6"/>
+      <c r="A887" s="8"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="6"/>
+      <c r="A888" s="8"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="6"/>
+      <c r="A889" s="8"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="6"/>
+      <c r="A890" s="8"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="6"/>
+      <c r="A891" s="8"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="6"/>
+      <c r="A892" s="8"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="6"/>
+      <c r="A893" s="8"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="6"/>
+      <c r="A894" s="8"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="6"/>
+      <c r="A895" s="8"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="6"/>
+      <c r="A896" s="8"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="6"/>
+      <c r="A897" s="8"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="6"/>
+      <c r="A898" s="8"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="6"/>
+      <c r="A899" s="8"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="6"/>
+      <c r="A900" s="8"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="6"/>
+      <c r="A901" s="8"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="6"/>
+      <c r="A902" s="8"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="6"/>
+      <c r="A903" s="8"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="6"/>
+      <c r="A904" s="8"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="6"/>
+      <c r="A905" s="8"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="6"/>
+      <c r="A906" s="8"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="6"/>
+      <c r="A907" s="8"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="6"/>
+      <c r="A908" s="8"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="6"/>
+      <c r="A909" s="8"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="6"/>
+      <c r="A910" s="8"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="6"/>
+      <c r="A911" s="8"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="6"/>
+      <c r="A912" s="8"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="6"/>
+      <c r="A913" s="8"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="6"/>
+      <c r="A914" s="8"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="6"/>
+      <c r="A915" s="8"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="6"/>
+      <c r="A916" s="8"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="6"/>
+      <c r="A917" s="8"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="6"/>
+      <c r="A918" s="8"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="6"/>
+      <c r="A919" s="8"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="6"/>
+      <c r="A920" s="8"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="6"/>
+      <c r="A921" s="8"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="6"/>
+      <c r="A922" s="8"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="6"/>
+      <c r="A923" s="8"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="6"/>
+      <c r="A924" s="8"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="6"/>
+      <c r="A925" s="8"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="6"/>
+      <c r="A926" s="8"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="6"/>
+      <c r="A927" s="8"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="6"/>
+      <c r="A928" s="8"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="6"/>
+      <c r="A929" s="8"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="6"/>
+      <c r="A930" s="8"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="6"/>
+      <c r="A931" s="8"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="6"/>
+      <c r="A932" s="8"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="6"/>
+      <c r="A933" s="8"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="6"/>
+      <c r="A934" s="8"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="6"/>
+      <c r="A935" s="8"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="6"/>
+      <c r="A936" s="8"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="6"/>
+      <c r="A937" s="8"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="6"/>
+      <c r="A938" s="8"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="6"/>
+      <c r="A939" s="8"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="6"/>
+      <c r="A940" s="8"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="6"/>
+      <c r="A941" s="8"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="6"/>
+      <c r="A942" s="8"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="6"/>
+      <c r="A943" s="8"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="6"/>
+      <c r="A944" s="8"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="6"/>
+      <c r="A945" s="8"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="6"/>
+      <c r="A946" s="8"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="6"/>
+      <c r="A947" s="8"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="6"/>
+      <c r="A948" s="8"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="6"/>
+      <c r="A949" s="8"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="6"/>
+      <c r="A950" s="8"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="6"/>
+      <c r="A951" s="8"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="6"/>
+      <c r="A952" s="8"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="6"/>
+      <c r="A953" s="8"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="6"/>
+      <c r="A954" s="8"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="6"/>
+      <c r="A955" s="8"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="6"/>
+      <c r="A956" s="8"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="6"/>
+      <c r="A957" s="8"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="6"/>
+      <c r="A958" s="8"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="6"/>
+      <c r="A959" s="8"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="6"/>
+      <c r="A960" s="8"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="6"/>
+      <c r="A961" s="8"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="6"/>
+      <c r="A962" s="8"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="6"/>
+      <c r="A963" s="8"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="6"/>
+      <c r="A964" s="8"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="6"/>
+      <c r="A965" s="8"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="6"/>
+      <c r="A966" s="8"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="6"/>
+      <c r="A967" s="8"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="6"/>
+      <c r="A968" s="8"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="6"/>
+      <c r="A969" s="8"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="6"/>
+      <c r="A970" s="8"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="6"/>
+      <c r="A971" s="8"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="6"/>
+      <c r="A972" s="8"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="6"/>
+      <c r="A973" s="8"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="6"/>
+      <c r="A974" s="8"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="6"/>
+      <c r="A975" s="8"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="6"/>
+      <c r="A976" s="8"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="6"/>
+      <c r="A977" s="8"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="6"/>
+      <c r="A978" s="8"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="6"/>
+      <c r="A979" s="8"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="6"/>
+      <c r="A980" s="8"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="6"/>
+      <c r="A981" s="8"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="6"/>
+      <c r="A982" s="8"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="6"/>
+      <c r="A983" s="8"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="6"/>
+      <c r="A984" s="8"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="6"/>
+      <c r="A985" s="8"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="6"/>
+      <c r="A986" s="8"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="6"/>
+      <c r="A987" s="8"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="6"/>
+      <c r="A988" s="8"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="6"/>
+      <c r="A989" s="8"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="6"/>
+      <c r="A990" s="8"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="6"/>
+      <c r="A991" s="8"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="6"/>
+      <c r="A992" s="8"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="6"/>
+      <c r="A993" s="8"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="6"/>
+      <c r="A994" s="8"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="6"/>
+      <c r="A995" s="8"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="6"/>
+      <c r="A996" s="8"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="6"/>
+      <c r="A997" s="8"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="6"/>
+      <c r="A998" s="8"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="6"/>
+      <c r="A999" s="8"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="6"/>
+      <c r="A1000" s="8"/>
     </row>
   </sheetData>
   <dataValidations>
@@ -7362,22 +7369,22 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="7">
         <v>1.0</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="7">
         <v>19.1</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>20.0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="7">
         <v>10.9</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
         <v>234.0</v>
       </c>
       <c r="G4" s="4">
@@ -7458,22 +7465,22 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="7">
         <v>100.0</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="7">
         <v>20.1</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="7">
         <v>1.6</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="7">
         <v>0.0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="7">
         <v>86.0</v>
       </c>
       <c r="G8" s="4">
@@ -7554,22 +7561,22 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="7">
         <v>100.0</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="7">
         <v>10.0</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="7">
         <v>0.0</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="7">
         <v>0.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>41.0</v>
       </c>
       <c r="G12" s="4">
@@ -7626,22 +7633,22 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>100.0</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="7">
         <v>80.0</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="7">
         <v>0.0</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="7">
         <v>0.0</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>320.0</v>
       </c>
       <c r="G15" s="4">
@@ -7650,22 +7657,22 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="7">
         <v>4.0</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="7">
         <v>0.0</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
         <v>0.0</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="7">
         <v>2.0</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>15.0</v>
       </c>
       <c r="G16" s="4">
@@ -7698,19 +7705,19 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="7">
         <v>1.0</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="7">
         <v>21.0</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="7">
         <v>14.0</v>
       </c>
       <c r="F18" s="3">
@@ -7722,22 +7729,22 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="7">
         <v>1.0</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="7">
         <v>21.7</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="7">
         <v>15.0</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="7">
         <v>10.0</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <v>212.0</v>
       </c>
       <c r="G19" s="4">
@@ -7746,22 +7753,22 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="7">
         <v>1.0</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="7">
         <v>27.0</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="7">
         <v>3.7</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="7">
         <v>7.5</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
         <v>195.0</v>
       </c>
       <c r="G20" s="4">
@@ -7818,22 +7825,22 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="7">
         <v>100.0</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="7">
         <v>0.0</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="7">
         <v>24.8</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="7">
         <v>0.6</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <v>104.0</v>
       </c>
       <c r="G23" s="4">
@@ -7986,22 +7993,22 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="7">
         <v>100.0</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="7">
         <v>41.0</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="7">
         <v>13.0</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="7">
         <v>3.0</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="7">
         <v>247.0</v>
       </c>
       <c r="G30" s="4">
@@ -8010,22 +8017,22 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="7">
         <v>100.0</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="7">
         <v>41.1</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="7">
         <v>6.0</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="7">
         <v>0.8</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="7">
         <v>207.0</v>
       </c>
       <c r="G31" s="4">
@@ -8034,22 +8041,22 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="7">
         <v>1.0</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="7">
         <v>45.0</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="7">
         <v>7.0</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="7">
         <v>13.0</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="7">
         <v>325.0</v>
       </c>
       <c r="G32" s="4">
@@ -8106,22 +8113,22 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="7">
         <v>100.0</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="7">
         <v>0.0</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="7">
         <v>17.0</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="7">
         <v>22.0</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <v>274.0</v>
       </c>
       <c r="G35" s="4">
@@ -8178,22 +8185,22 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="7">
         <v>1.0</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="7">
         <v>23.0</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="7">
         <v>15.0</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="7">
         <v>8.9</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>212.0</v>
       </c>
       <c r="G38" s="4">
@@ -8226,22 +8233,22 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="7">
         <v>100.0</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="7">
         <v>5.0</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="7">
         <v>2.5</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="7">
         <v>0.2</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="7">
         <v>26.0</v>
       </c>
       <c r="G40" s="4">
@@ -8274,22 +8281,22 @@
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="7">
         <v>100.0</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="7">
         <v>45.0</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="7">
         <v>9.3</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="7">
         <v>1.4</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>236.0</v>
       </c>
       <c r="G42" s="4">
@@ -8322,22 +8329,22 @@
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="7">
         <v>100.0</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="7">
         <v>71.0</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="7">
         <v>11.0</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="7">
         <v>1.5</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="7">
         <v>349.0</v>
       </c>
       <c r="G44" s="4">
@@ -8418,22 +8425,22 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="7">
         <v>100.0</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="7">
         <v>1.5</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="7">
         <v>11.0</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="7">
         <v>5.0</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="7">
         <v>95.0</v>
       </c>
       <c r="G48" s="4">
@@ -8466,22 +8473,22 @@
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="7">
         <v>100.0</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="7">
         <v>3.3</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="7">
         <v>1.2</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="7">
         <v>0.2</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="7">
         <v>16.0</v>
       </c>
       <c r="G50" s="4">
@@ -8586,22 +8593,22 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="7">
         <v>1.0</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="7">
         <v>60.0</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="7">
         <v>20.0</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="7">
         <v>10.0</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="7">
         <v>455.0</v>
       </c>
       <c r="G55" s="4">
@@ -8610,22 +8617,22 @@
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="7">
         <v>1.0</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="7">
         <v>16.0</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="7">
         <v>18.0</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="7">
         <v>3.2</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="7">
         <v>185.0</v>
       </c>
       <c r="G56" s="4">
@@ -8634,22 +8641,22 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="7">
         <v>100.0</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="7">
         <v>29.8</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="7">
         <v>12.4</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="7">
         <v>0.9</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="7">
         <v>216.0</v>
       </c>
       <c r="G57" s="4">
@@ -8658,22 +8665,22 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="7">
         <v>100.0</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="7">
         <v>72.0</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="7">
         <v>16.0</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="7">
         <v>4.0</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="7">
         <v>397.0</v>
       </c>
       <c r="G58" s="4">
@@ -8682,22 +8689,22 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="7">
         <v>100.0</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="7">
         <v>63.0</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="7">
         <v>9.0</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="7">
         <v>15.0</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="7">
         <v>435.0</v>
       </c>
       <c r="G59" s="4">

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
   <si>
     <t>מאכל</t>
   </si>
@@ -106,10 +106,13 @@
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
-    <t>פיתות כוסמין מלא</t>
+    <t>קוואקר</t>
   </si>
   <si>
-    <t>קוואקר</t>
+    <t>נודלס אורז</t>
+  </si>
+  <si>
+    <t>טופו קשה</t>
   </si>
   <si>
     <t>פסטרמה</t>
@@ -169,9 +172,6 @@
     <t>טונה</t>
   </si>
   <si>
-    <t>טופו קשה</t>
-  </si>
-  <si>
     <t>יוגור פרו אחוז וחצי</t>
   </si>
   <si>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>מנה חמה בקר</t>
-  </si>
-  <si>
-    <t>נודלס אורז</t>
   </si>
   <si>
     <t>נודלס חיטה</t>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>פיתות כוסמין לבן</t>
+  </si>
+  <si>
+    <t>פיתות כוסמין מלא</t>
   </si>
   <si>
     <t>פסטה אוסם</t>
@@ -595,23 +595,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>387.7014</v>
+        <v>412.113</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>211.863</v>
+        <v>204.365</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>63.717</v>
+        <v>60.225</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3023.26</v>
+        <v>3058.3</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2971.7106</v>
+        <v>3007.937</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -763,23 +763,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>221.0</v>
+        <v>195.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>20.6414</v>
+        <v>18.213</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.431</v>
+        <v>2.145</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.221</v>
+        <v>0.195</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>88.4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -787,23 +787,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="5">
-        <v>256.0</v>
+        <v>300.0</v>
       </c>
       <c r="C10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>51.2</v>
+        <v>60</v>
       </c>
       <c r="D10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>4.352</v>
+        <v>5.1</v>
       </c>
       <c r="E10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.256</v>
+        <v>0.3</v>
       </c>
       <c r="F10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>220.16</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -811,7 +811,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>200.0</v>
+        <v>170.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -819,15 +819,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>50</v>
+        <v>42.5</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -835,23 +835,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>28.16</v>
+        <v>35.2</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>141.2</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -859,15 +859,15 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>31.2</v>
+        <v>39</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>3.52</v>
+        <v>4.4</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
@@ -875,7 +875,7 @@
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>140</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -883,23 +883,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>25.2</v>
+        <v>31.5</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>174</v>
+        <v>217.5</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -1007,11 +1007,11 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="C19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 3, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 4, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F19" s="4">
         <f>VLOOKUP($A19, dict!$A:$F, 6, false) * $B19 / VLOOKUP($A19, dict!$A:$F, 2, false)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -1031,11 +1031,11 @@
         <v>13</v>
       </c>
       <c r="B20" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="C20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 3, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 4, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="F20" s="4">
         <f>VLOOKUP($A20, dict!$A:$F, 6, false) * $B20 / VLOOKUP($A20, dict!$A:$F, 2, false)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1103,7 +1103,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1111,44 +1111,44 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>20.8</v>
+        <v>15.6</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>17.2</v>
+        <v>12.9</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>236</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B24" s="7">
         <v>110.0</v>
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>37.4</v>
+        <v>41.8</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>8.8</v>
+        <v>10.56</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>217.8</v>
+        <v>237.6</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="7">
         <v>0.0</v>
@@ -1171,10 +1171,52 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4"/>
+      <c r="A26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="4">
+        <f>VLOOKUP($A26, dict!$A:$F, 3, false) * $B26 / VLOOKUP($A26, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <f>VLOOKUP($A26, dict!$A:$F, 4, false) * $B26 / VLOOKUP($A26, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <f>VLOOKUP($A26, dict!$A:$F, 5, false) * $B26 / VLOOKUP($A26, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="4">
+        <f>VLOOKUP($A26, dict!$A:$F, 6, false) * $B26 / VLOOKUP($A26, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4"/>
+      <c r="A27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="4">
+        <f>VLOOKUP($A27, dict!$A:$F, 3, false) * $B27 / VLOOKUP($A27, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <f>VLOOKUP($A27, dict!$A:$F, 4, false) * $B27 / VLOOKUP($A27, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="4">
+        <f>VLOOKUP($A27, dict!$A:$F, 5, false) * $B27 / VLOOKUP($A27, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <f>VLOOKUP($A27, dict!$A:$F, 6, false) * $B27 / VLOOKUP($A27, dict!$A:$F, 2, false)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
@@ -4275,7 +4317,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -4299,7 +4341,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -7303,10 +7345,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7321,12 +7363,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -7346,7 +7388,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -7370,7 +7412,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7">
         <v>1.0</v>
@@ -7442,7 +7484,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -7466,7 +7508,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7">
         <v>100.0</v>
@@ -7562,7 +7604,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7">
         <v>100.0</v>
@@ -7586,7 +7628,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4">
         <v>100.0</v>
@@ -7610,7 +7652,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7658,7 +7700,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="7">
         <v>4.0</v>
@@ -7706,7 +7748,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7">
         <v>1.0</v>
@@ -7730,7 +7772,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7">
         <v>1.0</v>
@@ -7754,7 +7796,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="7">
         <v>1.0</v>
@@ -7778,7 +7820,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7802,7 +7844,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7826,7 +7868,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7">
         <v>100.0</v>
@@ -7850,7 +7892,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -8066,7 +8108,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8090,7 +8132,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8114,7 +8156,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="7">
         <v>100.0</v>
@@ -8138,7 +8180,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8210,7 +8252,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8234,7 +8276,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B40" s="7">
         <v>100.0</v>
@@ -8282,7 +8324,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="7">
         <v>100.0</v>
@@ -8306,7 +8348,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8354,7 +8396,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>
@@ -8402,7 +8444,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" s="4">
         <v>100.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -88,7 +88,7 @@
     <t>אורז</t>
   </si>
   <si>
-    <t xml:space="preserve">גרנולה שוקולד </t>
+    <t>קוואקר</t>
   </si>
   <si>
     <t>דבש</t>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>אצבעות מוצרלה</t>
-  </si>
-  <si>
-    <t>קוואקר</t>
   </si>
   <si>
     <t>נודלס אורז</t>
@@ -236,6 +233,9 @@
   </si>
   <si>
     <t>פיתות כוסמין לוי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גרנולה שוקולד </t>
   </si>
 </sst>
 </file>
@@ -595,23 +595,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>412.113</v>
+        <v>401.128</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>204.365</v>
+        <v>215.49</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>60.225</v>
+        <v>57.04</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3058.3</v>
+        <v>3015.45</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>3007.937</v>
+        <v>2979.832</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -763,23 +763,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>195.0</v>
+        <v>220.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>18.213</v>
+        <v>20.548</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.145</v>
+        <v>2.42</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.195</v>
+        <v>0.22</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -787,23 +787,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="5">
-        <v>300.0</v>
+        <v>270.0</v>
       </c>
       <c r="C10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>5.1</v>
+        <v>4.59</v>
       </c>
       <c r="E10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>258</v>
+        <v>232.2</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -811,7 +811,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>170.0</v>
+        <v>220.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -819,15 +819,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>42.5</v>
+        <v>55</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>204</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -835,23 +835,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>35.2</v>
+        <v>31.68</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>176.5</v>
+        <v>158.85</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -859,15 +859,15 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>39</v>
+        <v>35.1</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>4.4</v>
+        <v>3.96</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
@@ -875,7 +875,7 @@
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>175</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -883,23 +883,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>31.5</v>
+        <v>27.6</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>217.5</v>
+        <v>149.6</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -933,11 +933,11 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="C16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 3, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 4, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
@@ -949,7 +949,7 @@
       </c>
       <c r="F16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 6, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>0.0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="7">
         <v>0.0</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="7">
         <v>0.0</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -7345,10 +7345,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7363,12 +7363,12 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="7">
         <v>1.0</v>
@@ -7484,7 +7484,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="7">
         <v>100.0</v>
@@ -7604,7 +7604,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7">
         <v>100.0</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4">
         <v>100.0</v>
@@ -7652,7 +7652,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4">
         <v>100.0</v>
@@ -7700,7 +7700,7 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7">
         <v>4.0</v>
@@ -7748,7 +7748,7 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="7">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="7">
         <v>1.0</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="7">
         <v>1.0</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="4">
         <v>1.0</v>
@@ -7844,7 +7844,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="4">
         <v>100.0</v>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="7">
         <v>100.0</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4">
         <v>100.0</v>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4">
         <v>1.0</v>
@@ -7988,7 +7988,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
@@ -8036,7 +8036,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30" s="7">
         <v>100.0</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" s="7">
         <v>100.0</v>
@@ -8084,7 +8084,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="7">
         <v>1.0</v>
@@ -8108,7 +8108,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="4">
         <v>100.0</v>
@@ -8132,7 +8132,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" s="4">
         <v>100.0</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="7">
         <v>100.0</v>
@@ -8180,7 +8180,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="4">
         <v>100.0</v>
@@ -8252,7 +8252,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="4">
         <v>100.0</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="7">
         <v>100.0</v>
@@ -8324,7 +8324,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" s="7">
         <v>100.0</v>
@@ -8348,7 +8348,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" s="3">
         <v>100.0</v>
@@ -8372,7 +8372,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" s="7">
         <v>100.0</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="4">
         <v>1.0</v>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="4">
         <v>100.0</v>
@@ -8444,7 +8444,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B47" s="4">
         <v>100.0</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="7">
         <v>100.0</v>
@@ -8492,7 +8492,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B49" s="4">
         <v>100.0</v>
@@ -8516,7 +8516,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" s="7">
         <v>100.0</v>
@@ -8540,7 +8540,7 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="4">
         <v>100.0</v>
@@ -8588,7 +8588,7 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="4">
         <v>100.0</v>
@@ -8636,7 +8636,7 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B55" s="7">
         <v>1.0</v>
@@ -8660,7 +8660,7 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B56" s="7">
         <v>1.0</v>
@@ -8684,7 +8684,7 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B57" s="7">
         <v>100.0</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="9" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="B59" s="7">
         <v>100.0</v>

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -595,23 +595,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>401.128</v>
+        <v>422.604</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>215.49</v>
+        <v>203.57</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>57.04</v>
+        <v>52.82</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3015.45</v>
+        <v>3014.95</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2979.832</v>
+        <v>2980.076</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -763,23 +763,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>220.0</v>
+        <v>260.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>20.548</v>
+        <v>24.284</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -787,23 +787,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="5">
-        <v>270.0</v>
+        <v>250.0</v>
       </c>
       <c r="C10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>4.59</v>
+        <v>4.25</v>
       </c>
       <c r="E10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>232.2</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -811,7 +811,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>220.0</v>
+        <v>180.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -819,15 +819,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>264</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -835,23 +835,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>45.0</v>
+        <v>55.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>31.68</v>
+        <v>38.72</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>158.85</v>
+        <v>194.15</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -859,15 +859,15 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>45.0</v>
+        <v>55.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>35.1</v>
+        <v>42.9</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>3.96</v>
+        <v>4.84</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
@@ -875,7 +875,7 @@
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>157.5</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -883,23 +883,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>27.6</v>
+        <v>34.5</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>149.6</v>
+        <v>187</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -1103,7 +1103,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 3, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
@@ -1111,15 +1111,15 @@
       </c>
       <c r="D23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 4, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="E23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 5, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>12.9</v>
+        <v>8.6</v>
       </c>
       <c r="F23" s="4">
         <f>VLOOKUP($A23, dict!$A:$F, 6, false) * $B23 / VLOOKUP($A23, dict!$A:$F, 2, false)</f>
-        <v>177</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">

--- a/macros.xlsx
+++ b/macros.xlsx
@@ -8,7 +8,7 @@
     <sheet state="visible" name="dict" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$59</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">dict!$A$1:$G$62</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="75">
   <si>
     <t>מאכל</t>
   </si>
@@ -58,7 +58,7 @@
     <t>יוגורט פרו זירו</t>
   </si>
   <si>
-    <t>פיתות כוסמין אנג'ל</t>
+    <t>פיתות כוסמין לבן</t>
   </si>
   <si>
     <t>עגלפפון</t>
@@ -82,10 +82,10 @@
     <t>חזה עוף</t>
   </si>
   <si>
-    <t>כוסמת</t>
+    <t>תערובת ירוקים</t>
   </si>
   <si>
-    <t>אורז</t>
+    <t>פסטה אוסם</t>
   </si>
   <si>
     <t>קוואקר</t>
@@ -97,7 +97,7 @@
     <t>בננה</t>
   </si>
   <si>
-    <t>יוגורט פרו מתוק</t>
+    <t>יוגורט סויה</t>
   </si>
   <si>
     <t>גיינר</t>
@@ -106,13 +106,13 @@
     <t>אצבעות מוצרלה</t>
   </si>
   <si>
-    <t>נודלס אורז</t>
-  </si>
-  <si>
     <t>טופו קשה</t>
   </si>
   <si>
-    <t>פסטרמה</t>
+    <t>טבורוג שלוש אחוז</t>
+  </si>
+  <si>
+    <t>קמח חיטה</t>
   </si>
   <si>
     <t>_</t>
@@ -133,6 +133,9 @@
     <t>אולין בוטנים קרמל</t>
   </si>
   <si>
+    <t>אורז</t>
+  </si>
+  <si>
     <t>אצבעות עמק</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>גרנולה לא מתוקה</t>
   </si>
   <si>
+    <t xml:space="preserve">גרנולה שוקולד </t>
+  </si>
+  <si>
     <t>זית</t>
   </si>
   <si>
@@ -157,13 +163,13 @@
     <t>חטיף חלבון פיסטוק</t>
   </si>
   <si>
+    <t>חטיף טודיי</t>
+  </si>
+  <si>
     <t>חטיף נטור ואלי</t>
   </si>
   <si>
     <t>חלבון ביצה</t>
-  </si>
-  <si>
-    <t>טבורוג שלוש אחוז</t>
   </si>
   <si>
     <t>טונה</t>
@@ -172,7 +178,13 @@
     <t>יוגור פרו אחוז וחצי</t>
   </si>
   <si>
+    <t>יוגורט פרו מתוק</t>
+  </si>
+  <si>
     <t>כדור תמרים</t>
+  </si>
+  <si>
+    <t>כוסמת</t>
   </si>
   <si>
     <t>לחם מלא</t>
@@ -181,7 +193,13 @@
     <t>לחם שחור משרד</t>
   </si>
   <si>
+    <t>לחמנייה ברון</t>
+  </si>
+  <si>
     <t>מנה חמה בקר</t>
+  </si>
+  <si>
+    <t>נודלס אורז</t>
   </si>
   <si>
     <t>נודלס חיטה</t>
@@ -199,13 +217,16 @@
     <t>פטריות פורטבלה</t>
   </si>
   <si>
-    <t>פיתות כוסמין לבן</t>
+    <t>פיתות כוסמין אנג'ל</t>
+  </si>
+  <si>
+    <t>פיתות כוסמין לוי</t>
   </si>
   <si>
     <t>פיתות כוסמין מלא</t>
   </si>
   <si>
-    <t>פסטה אוסם</t>
+    <t>פסטרמה</t>
   </si>
   <si>
     <t>פרגית</t>
@@ -220,22 +241,10 @@
     <t>קישוא</t>
   </si>
   <si>
-    <t>קמח חיטה</t>
-  </si>
-  <si>
-    <t>תערובת ירוקים</t>
-  </si>
-  <si>
     <t>ריבר בוט בינוני</t>
   </si>
   <si>
-    <t>חטיף טודיי</t>
-  </si>
-  <si>
-    <t>פיתות כוסמין לוי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרנולה שוקולד </t>
+    <t>מצת כוסמין</t>
   </si>
 </sst>
 </file>
@@ -595,23 +604,23 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>422.604</v>
+        <v>491.48</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>203.57</v>
+        <v>228.18</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>52.82</v>
+        <v>65.34</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>3014.95</v>
+        <v>3524.2</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>2980.076</v>
+        <v>3466.7</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -619,23 +628,23 @@
         <v>12</v>
       </c>
       <c r="B3" s="3">
-        <v>110.0</v>
+        <v>150.0</v>
       </c>
       <c r="C3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 3, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>67.5</v>
       </c>
       <c r="D3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 4, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>13.95</v>
       </c>
       <c r="E3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 5, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="F3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 6, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -715,7 +724,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="C7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 3, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
@@ -727,11 +736,11 @@
       </c>
       <c r="E7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 5, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>6.44</v>
+        <v>4.6</v>
       </c>
       <c r="F7" s="4">
         <f>VLOOKUP($A7, dict!$A:$F, 6, false) * $B7 / VLOOKUP($A7, dict!$A:$F, 2, false)</f>
-        <v>58.1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -763,23 +772,23 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>260.0</v>
+        <v>200.0</v>
       </c>
       <c r="C9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 3, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>24.284</v>
+        <v>18.68</v>
       </c>
       <c r="D9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 4, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="E9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 5, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="4">
         <f>VLOOKUP($A9, dict!$A:$F, 6, false) * $B9 / VLOOKUP($A9, dict!$A:$F, 2, false)</f>
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -787,23 +796,23 @@
         <v>18</v>
       </c>
       <c r="B10" s="5">
-        <v>250.0</v>
+        <v>0.0</v>
       </c>
       <c r="C10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 3, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 4, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 5, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
         <f>VLOOKUP($A10, dict!$A:$F, 6, false) * $B10 / VLOOKUP($A10, dict!$A:$F, 2, false)</f>
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -811,7 +820,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>180.0</v>
+        <v>230.0</v>
       </c>
       <c r="C11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 3, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
@@ -819,15 +828,15 @@
       </c>
       <c r="D11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 4, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>45</v>
+        <v>57.5</v>
       </c>
       <c r="E11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 5, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="F11" s="4">
         <f>VLOOKUP($A11, dict!$A:$F, 6, false) * $B11 / VLOOKUP($A11, dict!$A:$F, 2, false)</f>
-        <v>216</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -835,23 +844,23 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="C12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 3, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>38.72</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 4, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 5, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4">
         <f>VLOOKUP($A12, dict!$A:$F, 6, false) * $B12 / VLOOKUP($A12, dict!$A:$F, 2, false)</f>
-        <v>194.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -859,23 +868,23 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>55.0</v>
+        <v>150.0</v>
       </c>
       <c r="C13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 3, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>42.9</v>
+        <v>106.5</v>
       </c>
       <c r="D13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 4, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>4.84</v>
+        <v>16.5</v>
       </c>
       <c r="E13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 5, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="F13" s="4">
         <f>VLOOKUP($A13, dict!$A:$F, 6, false) * $B13 / VLOOKUP($A13, dict!$A:$F, 2, false)</f>
-        <v>192.5</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -883,23 +892,23 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="C14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 3, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>34.5</v>
+        <v>27.6</v>
       </c>
       <c r="D14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 4, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="E14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 5, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F14" s="4">
         <f>VLOOKUP($A14, dict!$A:$F, 6, false) * $B14 / VLOOKUP($A14, dict!$A:$F, 2, false)</f>
-        <v>187</v>
+        <v>149.6</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -933,11 +942,11 @@
         <v>23</v>
       </c>
       <c r="B16" s="3">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="C16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 3, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 4, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
@@ -949,7 +958,7 @@
       </c>
       <c r="F16" s="4">
         <f>VLOOKUP($A16, dict!$A:$F, 6, false) * $B16 / VLOOKUP($A16, dict!$A:$F, 2, false)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -987,7 +996,7 @@
       </c>
       <c r="C18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 3, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 4, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
@@ -995,11 +1004,11 @@
       </c>
       <c r="E18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 5, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" s="4">
         <f>VLOOKUP($A18, dict!$A:$F, 6, false) * $B18 / VLOOKUP($A18, dict!$A:$F, 2, false)</f>
-        <v>130</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -1052,26 +1061,26 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B21" s="7">
         <v>1.0</v>
       </c>
       <c r="C21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 3, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="D21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 4, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 5, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4">
         <f>VLOOKUP($A21, dict!$A:$F, 6, false) * $B21 / VLOOKUP($A21, dict!$A:$F, 2, false)</f>
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1131,48 +1140,48 @@
       </c>
       <c r="C24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 3, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>49.5</v>
       </c>
       <c r="D24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 4, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>10.23</v>
       </c>
       <c r="E24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 5, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="F24" s="4">
         <f>VLOOKUP($A24, dict!$A:$F, 6, false) * $B24 / VLOOKUP($A24, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>259.6</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="7">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="C25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 3, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 4, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 5, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F25" s="4">
         <f>VLOOKUP($A25, dict!$A:$F, 6, false) * $B25 / VLOOKUP($A25, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B26" s="7">
         <v>0.0</v>
@@ -1196,7 +1205,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="7">
         <v>0.0</v>
@@ -4201,106 +4210,106 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
-        <v>110.0</v>
+        <v>250.0</v>
       </c>
       <c r="C2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 3, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>41.8</v>
+        <v>8.75</v>
       </c>
       <c r="D2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 4, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>10.56</v>
+        <v>38.5</v>
       </c>
       <c r="E2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 5, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="F2" s="4">
         <f>VLOOKUP($A2, dict!$A:$F, 6, false) * $B2 / VLOOKUP($A2, dict!$A:$F, 2, false)</f>
-        <v>237.6</v>
+        <v>257.5</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:J2" si="1">SUM(C:C)</f>
-        <v>57.5</v>
+        <v>70.85</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="1"/>
-        <v>49.56</v>
+        <v>55.32</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="1"/>
-        <v>9.97</v>
+        <v>19.4</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="1"/>
-        <v>530.1</v>
+        <v>683.2</v>
       </c>
       <c r="K2" s="4">
         <f>G2*4 + H2*4 + I2*9</f>
-        <v>517.97</v>
+        <v>679.28</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>1.0</v>
+        <v>80.0</v>
       </c>
       <c r="C3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 3, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>6.7</v>
+        <v>57.6</v>
       </c>
       <c r="D3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 4, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>21</v>
+        <v>8.32</v>
       </c>
       <c r="E3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 5, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="4">
         <f>VLOOKUP($A3, dict!$A:$F, 6, false) * $B3 / VLOOKUP($A3, dict!$A:$F, 2, false)</f>
-        <v>116</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="C4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 3, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 4, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 5, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="F4" s="4">
         <f>VLOOKUP($A4, dict!$A:$F, 6, false) * $B4 / VLOOKUP($A4, dict!$A:$F, 2, false)</f>
-        <v>41.5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="C5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 3, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 4, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
@@ -4308,35 +4317,35 @@
       </c>
       <c r="E5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 5, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="F5" s="4">
         <f>VLOOKUP($A5, dict!$A:$F, 6, false) * $B5 / VLOOKUP($A5, dict!$A:$F, 2, false)</f>
-        <v>15</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
       </c>
       <c r="C6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 3, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 4, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 5, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4">
         <f>VLOOKUP($A6, dict!$A:$F, 6, false) * $B6 / VLOOKUP($A6, dict!$A:$F, 2, false)</f>
-        <v>120</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -7406,7 +7415,7 @@
         <v>110.0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G59" si="1">4*C3 + 4*D3 + 9*E3</f>
+        <f t="shared" ref="G3:G62" si="1">4*C3 + 4*D3 + 9*E3</f>
         <v>113</v>
       </c>
     </row>
@@ -7436,7 +7445,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B5" s="4">
         <v>100.0</v>
@@ -7484,7 +7493,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -7508,7 +7517,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7">
         <v>100.0</v>
@@ -7604,7 +7613,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7">
         <v>100.0</v>
@@ -7627,27 +7636,27 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="A13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7">
         <v>100.0</v>
       </c>
-      <c r="C13" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="4">
-        <v>31.0</v>
+      <c r="C13" s="7">
+        <v>72.0</v>
+      </c>
+      <c r="D13" s="7">
+        <v>16.0</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="F13" s="7">
+        <v>397.0</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>30.7</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -7658,140 +7667,140 @@
         <v>100.0</v>
       </c>
       <c r="C14" s="4">
-        <v>51.8</v>
+        <v>6.0</v>
       </c>
       <c r="D14" s="4">
-        <v>14.7</v>
+        <v>1.0</v>
       </c>
       <c r="E14" s="4">
-        <v>14.5</v>
+        <v>0.3</v>
       </c>
       <c r="F14" s="4">
-        <v>384.0</v>
+        <v>31.0</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>396.5</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4">
         <v>100.0</v>
       </c>
-      <c r="C15" s="7">
-        <v>80.0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="7">
-        <v>320.0</v>
+      <c r="C15" s="4">
+        <v>51.8</v>
+      </c>
+      <c r="D15" s="4">
+        <v>14.7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="F15" s="4">
+        <v>384.0</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>396.5</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="7">
-        <v>4.0</v>
+        <v>100.0</v>
       </c>
       <c r="C16" s="7">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
       <c r="D16" s="7">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="E16" s="7">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="F16" s="7">
-        <v>15.0</v>
+        <v>435.0</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="4">
+      <c r="A17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="7">
         <v>100.0</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="7">
+        <v>80.0</v>
+      </c>
+      <c r="D17" s="7">
         <v>0.0</v>
       </c>
-      <c r="D17" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="F17" s="4">
-        <v>120.0</v>
+      <c r="E17" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>320.0</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>122.5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C18" s="7">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="D18" s="7">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="E18" s="7">
-        <v>14.0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>276.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>15.0</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>278</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C19" s="7">
-        <v>21.7</v>
-      </c>
-      <c r="D19" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="E19" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="F19" s="7">
-        <v>212.0</v>
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="4">
+        <v>120.0</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>236.8</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -7802,68 +7811,68 @@
         <v>1.0</v>
       </c>
       <c r="C20" s="7">
-        <v>27.0</v>
+        <v>17.0</v>
       </c>
       <c r="D20" s="7">
-        <v>3.7</v>
+        <v>21.0</v>
       </c>
       <c r="E20" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="F20" s="7">
-        <v>195.0</v>
+        <v>14.0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>276.0</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>190.3</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="7">
         <v>1.0</v>
       </c>
-      <c r="C21" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="D21" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="4">
-        <v>17.2</v>
+      <c r="C21" s="7">
+        <v>21.7</v>
+      </c>
+      <c r="D21" s="7">
+        <v>15.0</v>
+      </c>
+      <c r="E21" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="F21" s="7">
+        <v>212.0</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>16.1</v>
+        <v>236.8</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="4">
-        <v>100.0</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="D22" s="4">
-        <v>15.4</v>
-      </c>
-      <c r="E22" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F22" s="4">
-        <v>103.0</v>
+      <c r="B22" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C22" s="7">
+        <v>16.0</v>
+      </c>
+      <c r="D22" s="7">
+        <v>18.0</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="F22" s="7">
+        <v>185.0</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>102.6</v>
+        <v>164.8</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -7871,892 +7880,961 @@
         <v>48</v>
       </c>
       <c r="B23" s="7">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C23" s="7">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="D23" s="7">
-        <v>24.8</v>
+        <v>3.7</v>
       </c>
       <c r="E23" s="7">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="F23" s="7">
-        <v>104.0</v>
+        <v>195.0</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>104.6</v>
+        <v>190.3</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="4">
-        <v>1.0</v>
+        <v>0.2</v>
       </c>
       <c r="D24" s="4">
-        <v>16.0</v>
+        <v>3.6</v>
       </c>
       <c r="E24" s="4">
-        <v>8.0</v>
+        <v>0.1</v>
       </c>
       <c r="F24" s="4">
-        <v>140.0</v>
+        <v>17.2</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B25" s="4">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="C25" s="4">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="D25" s="4">
-        <v>21.0</v>
+        <v>15.4</v>
       </c>
       <c r="E25" s="4">
         <v>3.0</v>
       </c>
       <c r="F25" s="4">
-        <v>140.0</v>
+        <v>103.0</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>138.2</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="C26" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="D26" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="E26" s="4">
+      <c r="A26" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="C26" s="7">
         <v>0.0</v>
       </c>
-      <c r="F26" s="4">
-        <v>116.0</v>
+      <c r="D26" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="F26" s="7">
+        <v>104.0</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>110.8</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C27" s="4">
         <v>1.0</v>
       </c>
-      <c r="C27" s="4">
-        <v>11.2</v>
-      </c>
       <c r="D27" s="4">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E27" s="4">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="F27" s="4">
-        <v>130.0</v>
+        <v>140.0</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>124.8</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4">
         <v>1.0</v>
       </c>
       <c r="C28" s="4">
-        <v>15.0</v>
+        <v>6.8</v>
       </c>
       <c r="D28" s="4">
-        <v>3.0</v>
+        <v>21.0</v>
       </c>
       <c r="E28" s="4">
         <v>3.0</v>
       </c>
       <c r="F28" s="4">
-        <v>100.0</v>
+        <v>140.0</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B29" s="4">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C29" s="4">
-        <v>70.4</v>
+        <v>6.7</v>
       </c>
       <c r="D29" s="4">
-        <v>12.0</v>
+        <v>21.0</v>
       </c>
       <c r="E29" s="4">
-        <v>2.6</v>
+        <v>0.0</v>
       </c>
       <c r="F29" s="4">
-        <v>353.0</v>
+        <v>116.0</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>353</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="C30" s="7">
-        <v>41.0</v>
-      </c>
-      <c r="D30" s="7">
-        <v>13.0</v>
-      </c>
-      <c r="E30" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="F30" s="7">
-        <v>247.0</v>
+      <c r="A30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C30" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>130.0</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>243</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C31" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="D31" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E31" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F31" s="4">
         <v>100.0</v>
-      </c>
-      <c r="C31" s="7">
-        <v>41.1</v>
-      </c>
-      <c r="D31" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="F31" s="7">
-        <v>207.0</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>195.6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C32" s="7">
-        <v>45.0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="E32" s="7">
-        <v>13.0</v>
-      </c>
-      <c r="F32" s="7">
-        <v>325.0</v>
+      <c r="A32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C32" s="4">
+        <v>70.4</v>
+      </c>
+      <c r="D32" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="F32" s="4">
+        <v>353.0</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>325</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="4">
+      <c r="A33" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="7">
         <v>100.0</v>
       </c>
-      <c r="C33" s="4">
-        <v>78.6</v>
-      </c>
-      <c r="D33" s="4">
-        <v>6.4</v>
-      </c>
-      <c r="E33" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F33" s="4">
-        <v>351.0</v>
+      <c r="C33" s="7">
+        <v>41.0</v>
+      </c>
+      <c r="D33" s="7">
+        <v>13.0</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>247.0</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>347.2</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="4">
+      <c r="A34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="7">
         <v>100.0</v>
       </c>
-      <c r="C34" s="4">
-        <v>78.2</v>
-      </c>
-      <c r="D34" s="4">
-        <v>11.3</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="4">
-        <v>350.0</v>
+      <c r="C34" s="7">
+        <v>41.1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="F34" s="7">
+        <v>207.0</v>
       </c>
       <c r="G34" s="4">
         <f t="shared" si="1"/>
-        <v>358</v>
+        <v>195.6</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B35" s="7">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C35" s="7">
-        <v>0.0</v>
+        <v>68.0</v>
       </c>
       <c r="D35" s="7">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="E35" s="7">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="F35" s="7">
-        <v>274.0</v>
+        <v>360.0</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" si="1"/>
-        <v>266</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="4">
-        <v>100.0</v>
-      </c>
-      <c r="C36" s="4">
-        <v>76.0</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F36" s="4">
-        <v>304.0</v>
+      <c r="A36" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C36" s="7">
+        <v>45.0</v>
+      </c>
+      <c r="D36" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>13.0</v>
+      </c>
+      <c r="F36" s="7">
+        <v>325.0</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>304</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B37" s="4">
         <v>100.0</v>
       </c>
       <c r="C37" s="4">
-        <v>3.5</v>
+        <v>78.6</v>
       </c>
       <c r="D37" s="4">
-        <v>0.0</v>
+        <v>6.4</v>
       </c>
       <c r="E37" s="4">
-        <v>0.0</v>
+        <v>0.8</v>
       </c>
       <c r="F37" s="4">
-        <v>15.0</v>
+        <v>351.0</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="C38" s="7">
-        <v>23.0</v>
-      </c>
-      <c r="D38" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="E38" s="7">
-        <v>8.9</v>
-      </c>
-      <c r="F38" s="7">
-        <v>212.0</v>
+      <c r="A38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C38" s="4">
+        <v>78.2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>11.3</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F38" s="4">
+        <v>350.0</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="1"/>
-        <v>232.1</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="7">
         <v>100.0</v>
       </c>
-      <c r="C39" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="D39" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="E39" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="F39" s="4">
+      <c r="C39" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="D39" s="7">
+        <v>17.0</v>
+      </c>
+      <c r="E39" s="7">
         <v>22.0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>274.0</v>
       </c>
       <c r="G39" s="4">
         <f t="shared" si="1"/>
-        <v>27.9</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="7">
+      <c r="A40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="4">
         <v>100.0</v>
       </c>
-      <c r="C40" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="D40" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="F40" s="7">
-        <v>26.0</v>
+      <c r="C40" s="4">
+        <v>76.0</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>304.0</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>31.8</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" s="4">
         <v>100.0</v>
       </c>
       <c r="C41" s="4">
-        <v>38.0</v>
+        <v>3.5</v>
       </c>
       <c r="D41" s="4">
-        <v>9.6</v>
+        <v>0.0</v>
       </c>
       <c r="E41" s="4">
-        <v>1.7</v>
+        <v>0.0</v>
       </c>
       <c r="F41" s="4">
-        <v>216.0</v>
+        <v>15.0</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>205.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="B42" s="7">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C42" s="7">
-        <v>45.0</v>
+        <v>23.0</v>
       </c>
       <c r="D42" s="7">
-        <v>9.3</v>
+        <v>15.0</v>
       </c>
       <c r="E42" s="7">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="F42" s="7">
-        <v>236.0</v>
+        <v>212.0</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="1"/>
-        <v>229.8</v>
+        <v>232.1</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" s="3">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="4">
         <v>100.0</v>
       </c>
-      <c r="C43" s="3">
-        <v>34.0</v>
-      </c>
-      <c r="D43" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="F43" s="3">
-        <v>198.0</v>
+      <c r="C43" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="D43" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="F43" s="4">
+        <v>22.0</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="1"/>
-        <v>185.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B44" s="7">
         <v>100.0</v>
       </c>
       <c r="C44" s="7">
-        <v>71.0</v>
+        <v>5.0</v>
       </c>
       <c r="D44" s="7">
-        <v>11.0</v>
+        <v>2.5</v>
       </c>
       <c r="E44" s="7">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="F44" s="7">
-        <v>349.0</v>
+        <v>26.0</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>341.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B45" s="4">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="C45" s="4">
-        <v>1.1</v>
+        <v>38.0</v>
       </c>
       <c r="D45" s="4">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="E45" s="4">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="F45" s="4">
-        <v>24.0</v>
+        <v>216.0</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>25.1</v>
+        <v>205.7</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="4">
+      <c r="A46" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="7">
         <v>100.0</v>
       </c>
-      <c r="C46" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D46" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="E46" s="4">
-        <v>9.0</v>
-      </c>
-      <c r="F46" s="4">
-        <v>175.0</v>
+      <c r="C46" s="7">
+        <v>45.0</v>
+      </c>
+      <c r="D46" s="7">
+        <v>9.3</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="F46" s="7">
+        <v>236.0</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="1"/>
-        <v>173</v>
+        <v>229.8</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="4">
+      <c r="A47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="7">
         <v>100.0</v>
       </c>
-      <c r="C47" s="4">
-        <v>69.0</v>
-      </c>
-      <c r="D47" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="E47" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="F47" s="4">
-        <v>374.0</v>
+      <c r="C47" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="D47" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="F47" s="7">
+        <v>216.0</v>
       </c>
       <c r="G47" s="4">
         <f t="shared" si="1"/>
-        <v>392</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="7">
+      <c r="A48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="3">
         <v>100.0</v>
       </c>
-      <c r="C48" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D48" s="7">
-        <v>11.0</v>
-      </c>
-      <c r="E48" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="F48" s="7">
-        <v>95.0</v>
+      <c r="C48" s="3">
+        <v>34.0</v>
+      </c>
+      <c r="D48" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="F48" s="3">
+        <v>198.0</v>
       </c>
       <c r="G48" s="4">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>185.1</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" s="4">
+      <c r="A49" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="7">
         <v>100.0</v>
       </c>
-      <c r="C49" s="4">
-        <v>16.2</v>
-      </c>
-      <c r="D49" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="E49" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="F49" s="4">
-        <v>133.0</v>
+      <c r="C49" s="7">
+        <v>71.0</v>
+      </c>
+      <c r="D49" s="7">
+        <v>11.0</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="F49" s="7">
+        <v>349.0</v>
       </c>
       <c r="G49" s="4">
         <f t="shared" si="1"/>
-        <v>110.5</v>
+        <v>341.5</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="C50" s="7">
-        <v>3.3</v>
-      </c>
-      <c r="D50" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="F50" s="7">
-        <v>16.0</v>
+      <c r="A50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C50" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="D50" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F50" s="4">
+        <v>24.0</v>
       </c>
       <c r="G50" s="4">
         <f t="shared" si="1"/>
-        <v>19.8</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B51" s="4">
         <v>100.0</v>
       </c>
       <c r="C51" s="4">
-        <v>72.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" s="4">
-        <v>10.4</v>
+        <v>23.0</v>
       </c>
       <c r="E51" s="4">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="F51" s="4">
-        <v>339.0</v>
+        <v>175.0</v>
       </c>
       <c r="G51" s="4">
         <f t="shared" si="1"/>
-        <v>338.6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B52" s="4">
         <v>100.0</v>
       </c>
       <c r="C52" s="4">
-        <v>0.0</v>
+        <v>69.0</v>
       </c>
       <c r="D52" s="4">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="E52" s="4">
-        <v>92.0</v>
+        <v>8.0</v>
       </c>
       <c r="F52" s="4">
-        <v>830.0</v>
+        <v>374.0</v>
       </c>
       <c r="G52" s="4">
         <f t="shared" si="1"/>
-        <v>828</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="4">
+      <c r="A53" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="7">
         <v>100.0</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D53" s="7">
+        <v>11.0</v>
+      </c>
+      <c r="E53" s="7">
         <v>5.0</v>
       </c>
-      <c r="D53" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="E53" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F53" s="4">
-        <v>50.0</v>
+      <c r="F53" s="7">
+        <v>95.0</v>
       </c>
       <c r="G53" s="4">
         <f t="shared" si="1"/>
-        <v>43.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="B54" s="4">
         <v>100.0</v>
       </c>
       <c r="C54" s="4">
-        <v>20.0</v>
+        <v>16.2</v>
       </c>
       <c r="D54" s="4">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="E54" s="4">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F54" s="4">
-        <v>86.0</v>
+        <v>133.0</v>
       </c>
       <c r="G54" s="4">
         <f t="shared" si="1"/>
-        <v>87.7</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B55" s="7">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="C55" s="7">
-        <v>60.0</v>
+        <v>3.3</v>
       </c>
       <c r="D55" s="7">
-        <v>20.0</v>
+        <v>1.2</v>
       </c>
       <c r="E55" s="7">
-        <v>10.0</v>
+        <v>0.2</v>
       </c>
       <c r="F55" s="7">
-        <v>455.0</v>
+        <v>16.0</v>
       </c>
       <c r="G55" s="4">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56" s="7">
+      <c r="A56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C56" s="4">
+        <v>72.0</v>
+      </c>
+      <c r="D56" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="E56" s="4">
         <v>1.0</v>
       </c>
-      <c r="C56" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="D56" s="7">
-        <v>18.0</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="F56" s="7">
-        <v>185.0</v>
+      <c r="F56" s="4">
+        <v>339.0</v>
       </c>
       <c r="G56" s="4">
         <f t="shared" si="1"/>
-        <v>164.8</v>
+        <v>338.6</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B57" s="7">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="C57" s="7">
-        <v>29.8</v>
+        <v>60.0</v>
       </c>
       <c r="D57" s="7">
-        <v>12.4</v>
+        <v>20.0</v>
       </c>
       <c r="E57" s="7">
-        <v>0.9</v>
+        <v>10.0</v>
       </c>
       <c r="F57" s="7">
-        <v>216.0</v>
+        <v>455.0</v>
       </c>
       <c r="G57" s="4">
         <f t="shared" si="1"/>
-        <v>176.9</v>
+        <v>410</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B58" s="7">
+      <c r="A58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="4">
         <v>100.0</v>
       </c>
-      <c r="C58" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="D58" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="E58" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="F58" s="7">
-        <v>397.0</v>
+      <c r="C58" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E58" s="4">
+        <v>92.0</v>
+      </c>
+      <c r="F58" s="4">
+        <v>830.0</v>
       </c>
       <c r="G58" s="4">
         <f t="shared" si="1"/>
-        <v>388</v>
+        <v>828</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="7">
+      <c r="A59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="4">
         <v>100.0</v>
       </c>
-      <c r="C59" s="7">
-        <v>63.0</v>
-      </c>
-      <c r="D59" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="E59" s="7">
-        <v>15.0</v>
-      </c>
-      <c r="F59" s="7">
-        <v>435.0</v>
+      <c r="C59" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="D59" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F59" s="4">
+        <v>50.0</v>
       </c>
       <c r="G59" s="4">
         <f t="shared" si="1"/>
-        <v>423</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="4">
+        <v>100.0</v>
+      </c>
+      <c r="C60" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>86.0</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="1"/>
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="C61" s="7">
+        <v>71.0</v>
+      </c>
+      <c r="D61" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="F61" s="7">
+        <v>361.0</v>
+      </c>
+      <c r="G61" s="4">
+        <f t="shared" si="1"/>
+        <v>354.2</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="C62" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="D62" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="E62" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="F62" s="7">
+        <v>190.0</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
     <row r="63" ht="15.75" customHeight="1"/>
     <row r="64" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
@@ -9697,9 +9775,9 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$G$59">
-    <sortState ref="A1:G59">
-      <sortCondition ref="A1:A59"/>
+  <autoFilter ref="$A$1:$G$62">
+    <sortState ref="A1:G62">
+      <sortCondition ref="A1:A62"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
